--- a/data/output/workbook/2026-07-03.xlsx
+++ b/data/output/workbook/2026-07-03.xlsx
@@ -490,7 +490,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10344150"/>
+    <ext cx="10125075" cy="10763250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -953,7 +953,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03 04:06</t>
+          <t>2026-07-03 06:49</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q80"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2082,324 +2082,174 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="29" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
         <is>
           <t>Chicago White Sox offense vs Cleveland Guardians defense</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="30" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B67" s="30" t="inlineStr">
+      <c r="B69" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C67" s="30" t="inlineStr">
+      <c r="C69" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D67" s="30" t="inlineStr">
+      <c r="D69" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E67" s="30" t="inlineStr">
+      <c r="E69" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F67" s="30" t="inlineStr">
+      <c r="F69" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G67" s="30" t="inlineStr">
+      <c r="G69" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H67" s="30" t="inlineStr">
+      <c r="H69" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I67" s="30" t="inlineStr">
+      <c r="I69" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J67" s="30" t="inlineStr">
+      <c r="J69" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K67" s="30" t="inlineStr">
+      <c r="K69" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L67" s="30" t="inlineStr">
+      <c r="L69" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M67" s="30" t="inlineStr">
+      <c r="M69" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N67" s="30" t="inlineStr">
+      <c r="N69" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O67" s="30" t="inlineStr">
+      <c r="O69" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P67" s="30" t="inlineStr">
+      <c r="P69" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q67" s="30" t="inlineStr">
+      <c r="Q69" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B68" s="32" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="C68" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="D68" s="32" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="E68" s="32" t="n">
-        <v>5.333</v>
-      </c>
-      <c r="F68" s="32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="G68" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H68" s="33" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J68" s="33" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L68" s="32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="M68" s="32" t="n">
-        <v>4.267</v>
-      </c>
-      <c r="N68" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="O68" s="32" t="n">
-        <v>4.367</v>
-      </c>
-      <c r="P68" s="32" t="n">
-        <v>4.141</v>
-      </c>
-      <c r="Q68" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>7.792</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="D69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>7.939</v>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>1.354</v>
+        <v>4.933</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.1</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H70" s="33" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J70" s="33" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>4</v>
       </c>
       <c r="O70" s="32" t="n">
-        <v>0.75</v>
+        <v>4.367</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>1.143</v>
+        <v>4.141</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>9.208</v>
+        <v>7.792</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D71" s="32" t="inlineStr">
         <is>
@@ -2453,390 +2303,390 @@
         </is>
       </c>
       <c r="O71" s="32" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>9.388</v>
+        <v>7.939</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="n">
+        <v>1.354</v>
+      </c>
+      <c r="C72" s="32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P72" s="32" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="Q72" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>9.208</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>9.388</v>
+      </c>
+      <c r="Q73" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B72" s="32" t="n">
+      <c r="B74" s="32" t="n">
         <v>0.589</v>
       </c>
-      <c r="C72" s="32" t="n">
+      <c r="C74" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="D72" s="32" t="n">
+      <c r="D74" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="E72" s="32" t="n">
+      <c r="E74" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="F72" s="32" t="n">
+      <c r="F74" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="G72" s="32" t="n">
+      <c r="G74" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="H72" s="34" t="inlineStr">
+      <c r="H74" s="34" t="inlineStr">
         <is>
           <t>7th</t>
         </is>
       </c>
-      <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="34" t="inlineStr">
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="34" t="inlineStr">
         <is>
           <t>3rd</t>
         </is>
       </c>
-      <c r="K72" s="32" t="n">
+      <c r="K74" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L72" s="32" t="n">
+      <c r="L74" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="M72" s="32" t="n">
+      <c r="M74" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="N72" s="32" t="n">
+      <c r="N74" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="O72" s="32" t="n">
+      <c r="O74" s="32" t="n">
         <v>0.367</v>
       </c>
-      <c r="P72" s="32" t="n">
+      <c r="P74" s="32" t="n">
         <v>0.36</v>
       </c>
-      <c r="Q72" s="35" t="inlineStr">
+      <c r="Q74" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="29" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
         <is>
           <t>Cleveland Guardians offense vs Chicago White Sox defense</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="30" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B75" s="30" t="inlineStr">
+      <c r="B77" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C75" s="30" t="inlineStr">
+      <c r="C77" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D75" s="30" t="inlineStr">
+      <c r="D77" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E75" s="30" t="inlineStr">
+      <c r="E77" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F75" s="30" t="inlineStr">
+      <c r="F77" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G75" s="30" t="inlineStr">
+      <c r="G77" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H75" s="30" t="inlineStr">
+      <c r="H77" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I75" s="30" t="inlineStr">
+      <c r="I77" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J75" s="30" t="inlineStr">
+      <c r="J77" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K75" s="30" t="inlineStr">
+      <c r="K77" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L75" s="30" t="inlineStr">
+      <c r="L77" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M75" s="30" t="inlineStr">
+      <c r="M77" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N75" s="30" t="inlineStr">
+      <c r="N77" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O75" s="30" t="inlineStr">
+      <c r="O77" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P75" s="30" t="inlineStr">
+      <c r="P77" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q75" s="30" t="inlineStr">
+      <c r="Q77" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B76" s="32" t="n">
-        <v>3.949</v>
-      </c>
-      <c r="C76" s="32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D76" s="32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E76" s="32" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="F76" s="32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="G76" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H76" s="33" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="33" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L76" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M76" s="32" t="n">
-        <v>3.867</v>
-      </c>
-      <c r="N76" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O76" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="P76" s="32" t="n">
-        <v>4.733</v>
-      </c>
-      <c r="Q76" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>7.735</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="D77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>7.854</v>
-      </c>
-      <c r="Q77" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>0.959</v>
+        <v>3.949</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>3.7</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H78" s="33" t="inlineStr">
+        <is>
+          <t>13th</t>
         </is>
       </c>
       <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J78" s="33" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>3.867</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>4.2</v>
       </c>
       <c r="O78" s="32" t="n">
-        <v>0.6</v>
+        <v>4.3</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>1.062</v>
+        <v>4.733</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>8</v>
+        <v>7.735</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>11.25</v>
+        <v>9.75</v>
       </c>
       <c r="D79" s="32" t="inlineStr">
         <is>
@@ -2890,71 +2740,221 @@
         </is>
       </c>
       <c r="O79" s="32" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>7.938</v>
+        <v>7.854</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B80" s="32" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="C80" s="32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="32" t="inlineStr"/>
+      <c r="J80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O80" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P80" s="32" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="Q80" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="P81" s="32" t="n">
+        <v>7.938</v>
+      </c>
+      <c r="Q81" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B80" s="32" t="n">
+      <c r="B82" s="32" t="n">
         <v>0.507</v>
       </c>
-      <c r="C80" s="32" t="n">
+      <c r="C82" s="32" t="n">
         <v>0.367</v>
       </c>
-      <c r="D80" s="32" t="n">
+      <c r="D82" s="32" t="n">
         <v>0.25</v>
       </c>
-      <c r="E80" s="32" t="n">
+      <c r="E82" s="32" t="n">
         <v>0.267</v>
       </c>
-      <c r="F80" s="32" t="n">
+      <c r="F82" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="G80" s="32" t="n">
+      <c r="G82" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="H80" s="33" t="inlineStr">
+      <c r="H82" s="33" t="inlineStr">
         <is>
           <t>18th</t>
         </is>
       </c>
-      <c r="I80" s="32" t="inlineStr"/>
-      <c r="J80" s="33" t="inlineStr">
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="33" t="inlineStr">
         <is>
           <t>18th</t>
         </is>
       </c>
-      <c r="K80" s="32" t="n">
+      <c r="K82" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="L80" s="32" t="n">
+      <c r="L82" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="M80" s="32" t="n">
+      <c r="M82" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="N80" s="32" t="n">
+      <c r="N82" s="32" t="n">
         <v>0.55</v>
       </c>
-      <c r="O80" s="32" t="n">
+      <c r="O82" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="P80" s="32" t="n">
+      <c r="P82" s="32" t="n">
         <v>0.548</v>
       </c>
-      <c r="Q80" s="35" t="inlineStr">
+      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7747,13 +7747,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6952962962962962</v>
+        <v>0.6928897338403042</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-228</v>
+        <v>-226</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 69.5% (fair -228). Your call.</t>
+          <t>Model 69.3% (fair -226). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -7879,10 +7879,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6199629629629629</v>
+        <v>0.6174444444444445</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-163</v>
+        <v>-161</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>170</v>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 62.0% (fair -163). Your call.</t>
+          <t>Model 61.7% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -8058,12 +8058,12 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -8073,17 +8073,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins +1.5</t>
+          <t>Pittsburgh Pirates +1.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.59</v>
+        <v>0.6663156398104265</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-144</v>
+        <v>-200</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>128</v>
+        <v>-111</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8107,7 +8107,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 66.6% (fair -200). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8124,12 +8124,12 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>01:38</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -8139,17 +8139,17 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates +1.5</t>
+          <t>Los Angeles Angels -1.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.6662943396226416</v>
+        <v>0.4010958904109589</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-200</v>
+        <v>149</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-112</v>
+        <v>192</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 66.6% (fair -200). Your call.</t>
+          <t>Model 40.1% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8209,13 +8209,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5353153153153154</v>
+        <v>0.5352995391705069</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>-115</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8251,37 +8251,37 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Los Angeles Angels</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>01:38</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels -1.5</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4010958904109589</v>
+        <v>0.485793991416309</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>149</v>
+        <v>106</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>192</v>
+        <v>133</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 40.1% (fair +149). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8317,37 +8317,37 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>Miami Marlins @ Athletics</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Athletics -1.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5913622119815668</v>
+        <v>0.4242585551330798</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-145</v>
+        <v>136</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-117</v>
+        <v>163</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 59.1% (fair -145). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8388,12 +8388,12 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -8403,17 +8403,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.475304347826087</v>
+        <v>0.3972661870503597</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>130</v>
+        <v>178</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8437,7 +8437,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 47.5% (fair +110). Your call.</t>
+          <t>Model 39.7% (fair +152). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8454,12 +8454,12 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -8469,17 +8469,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4005514705882353</v>
+        <v>0.4732618025751073</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>150</v>
+        <v>111</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>172</v>
+        <v>133</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8503,7 +8503,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 40.1% (fair +150). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8530,22 +8530,22 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Athletics -1.5</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4242578125</v>
+        <v>0.5310294117647059</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>136</v>
+        <v>-113</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>156</v>
+        <v>104</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8581,37 +8581,37 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs -1.5</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.423984375</v>
+        <v>0.5944477477477478</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>136</v>
+        <v>-147</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>156</v>
+        <v>-122</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 59.4% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -8652,32 +8652,32 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Athletics</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5310294117647059</v>
+        <v>0.5724272300469483</v>
       </c>
       <c r="G19" s="14" t="n">
+        <v>-134</v>
+      </c>
+      <c r="H19" s="15" t="n">
         <v>-113</v>
-      </c>
-      <c r="H19" s="15" t="n">
-        <v>104</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -8713,17 +8713,17 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5739657276995306</v>
+        <v>0.4073003802281369</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-135</v>
+        <v>146</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-113</v>
+        <v>163</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 57.4% (fair -135). Your call.</t>
+          <t>Model 40.7% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -8803,10 +8803,10 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.421015625</v>
+        <v>0.4183984374999999</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>156</v>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 42.1% (fair +138). Your call.</t>
+          <t>Model 41.8% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -8845,37 +8845,37 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4079087452471483</v>
+        <v>0.53225</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>145</v>
+        <v>-114</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -8899,7 +8899,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 40.8% (fair +145). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -8916,32 +8916,32 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Colorado Rockies</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Chicago Cubs -1.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4358606557377049</v>
+        <v>0.42496</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -8965,7 +8965,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 43.6% (fair +129). Your call.</t>
+          <t>Model 42.5% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -8982,32 +8982,32 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5345910891089108</v>
+        <v>0.509326923076923</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-115</v>
+        <v>-104</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-102</v>
+        <v>108</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -9031,7 +9031,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9048,32 +9048,32 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>00:15</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5086538461538461</v>
+        <v>0.5117156862745098</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-104</v>
+        <v>-105</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -9133,13 +9133,13 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5508352112676056</v>
+        <v>0.5501207547169812</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-123</v>
+        <v>-122</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-113</v>
+        <v>-112</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -9163,7 +9163,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 55.0% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -9180,32 +9180,32 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>San Francisco Giants @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5085784313725491</v>
+        <v>0.4370168067226891</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-103</v>
+        <v>129</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -9229,7 +9229,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -103). Your call.</t>
+          <t>Model 43.7% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -9246,32 +9246,32 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals +1.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5759761061946903</v>
+        <v>0.5300941176470588</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-136</v>
+        <v>-113</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-126</v>
+        <v>-104</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -9295,7 +9295,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -9312,32 +9312,32 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Minnesota Twins +1.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5065517241379309</v>
+        <v>0.5519943925233645</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-103</v>
+        <v>-123</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>103</v>
+        <v>-114</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -9361,7 +9361,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -9538,13 +9538,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4561111111111111</v>
+        <v>0.4550691244239632</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +119). Your call.</t>
+          <t>Model 45.5% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -9604,10 +9604,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5439152073732718</v>
+        <v>0.5449396313364054</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-119</v>
+        <v>-120</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>-117</v>
@@ -9634,7 +9634,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -119). Your call.</t>
+          <t>Model 54.5% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.46545</v>
+        <v>0.46775</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>100</v>
@@ -9700,7 +9700,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9736,13 +9736,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5345910891089108</v>
+        <v>0.53225</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-115</v>
+        <v>-114</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-102</v>
+        <v>100</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9802,13 +9802,13 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.423984375</v>
+        <v>0.42496</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9832,7 +9832,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 42.5% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9868,13 +9868,13 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5759761061946903</v>
+        <v>0.5750246696035243</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-136</v>
+        <v>-135</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-126</v>
+        <v>-127</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 57.5% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9934,13 +9934,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.475304347826087</v>
+        <v>0.4732618025751073</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 47.5% (fair +110). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -10000,10 +10000,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5246935622317597</v>
+        <v>0.5267484978540773</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-110</v>
+        <v>-111</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>-133</v>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 52.5% (fair -110). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -10066,10 +10066,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5769</v>
+        <v>0.5300941176470588</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-136</v>
+        <v>-113</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>-104</v>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -10132,13 +10132,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4231</v>
+        <v>0.46995</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -10162,7 +10162,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +136). Your call.</t>
+          <t>Model 47.0% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -10264,13 +10264,13 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.6662943396226416</v>
+        <v>0.6663156398104265</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>-200</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-112</v>
+        <v>-111</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -10330,13 +10330,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4005514705882353</v>
+        <v>0.3972661870503597</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -10360,7 +10360,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 40.1% (fair +150). Your call.</t>
+          <t>Model 39.7% (fair +152). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -10396,10 +10396,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5994744525547445</v>
+        <v>0.6027131386861314</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-150</v>
+        <v>-152</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>-174</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 59.9% (fair -150). Your call.</t>
+          <t>Model 60.3% (fair -152). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -10468,7 +10468,7 @@
         <v>121</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>105</v>
+        <v>-102</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -10534,7 +10534,7 @@
         <v>-121</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -10594,10 +10594,10 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.41</v>
+        <v>0.447981220657277</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>113</v>
@@ -10624,7 +10624,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 41.0% (fair +144). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -10660,13 +10660,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.59</v>
+        <v>0.5519943925233645</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-144</v>
+        <v>-123</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>128</v>
+        <v>-114</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -10690,7 +10690,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10726,10 +10726,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5739657276995306</v>
+        <v>0.5724272300469483</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-135</v>
+        <v>-134</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>-113</v>
@@ -10756,7 +10756,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 57.4% (fair -135). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10792,13 +10792,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.426056338028169</v>
+        <v>0.4275829383886255</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10822,7 +10822,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 42.6% (fair +135). Your call.</t>
+          <t>Model 42.8% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10864,7 +10864,7 @@
         <v>-113</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10990,13 +10990,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4582511210762332</v>
+        <v>0.4543859649122807</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -11020,7 +11020,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 45.8% (fair +118). Your call.</t>
+          <t>Model 45.4% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -11056,10 +11056,10 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5417361233480177</v>
+        <v>0.5456524229074891</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-118</v>
+        <v>-120</v>
       </c>
       <c r="H28" s="15" t="n">
         <v>-127</v>
@@ -11086,7 +11086,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -118). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5347</v>
+        <v>0.5354</v>
       </c>
       <c r="G29" s="14" t="n">
         <v>-115</v>
@@ -11188,7 +11188,7 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.4653</v>
+        <v>0.4646</v>
       </c>
       <c r="G30" s="14" t="n">
         <v>115</v>
@@ -11254,10 +11254,10 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.3800380228136883</v>
+        <v>0.3825475285171103</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H31" s="15" t="n">
         <v>163</v>
@@ -11284,7 +11284,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 38.0% (fair +163). Your call.</t>
+          <t>Model 38.3% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -11320,10 +11320,10 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.6199629629629629</v>
+        <v>0.6174444444444445</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-163</v>
+        <v>-161</v>
       </c>
       <c r="H32" s="15" t="n">
         <v>170</v>
@@ -11350,7 +11350,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 62.0% (fair -163). Your call.</t>
+          <t>Model 61.7% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -11386,7 +11386,7 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.5086538461538461</v>
+        <v>0.509326923076923</v>
       </c>
       <c r="G33" s="14" t="n">
         <v>-104</v>
@@ -11452,7 +11452,7 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.4913480769230769</v>
+        <v>0.4906730769230769</v>
       </c>
       <c r="G34" s="14" t="n">
         <v>104</v>
@@ -11518,13 +11518,13 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.3603</v>
+        <v>0.4016</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>178</v>
+        <v>149</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -11548,7 +11548,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 36.0% (fair +178). Your call.</t>
+          <t>Model 40.2% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -11584,13 +11584,13 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.6396999999999999</v>
+        <v>0.5984</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-178</v>
+        <v>-149</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -11614,7 +11614,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 64.0% (fair -178). Your call.</t>
+          <t>Model 59.8% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -11650,10 +11650,10 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.3047037037037037</v>
+        <v>0.3071111111111111</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H37" s="15" t="n">
         <v>170</v>
@@ -11680,7 +11680,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 30.5% (fair +228). Your call.</t>
+          <t>Model 30.7% (fair +226). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -11716,13 +11716,13 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.6952962962962962</v>
+        <v>0.6928897338403042</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-228</v>
+        <v>-226</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -11746,7 +11746,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 69.5% (fair -228). Your call.</t>
+          <t>Model 69.3% (fair -226). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -11782,13 +11782,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.564118487394958</v>
+        <v>0.5629573770491804</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>-129</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>-138</v>
+        <v>-144</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -11812,7 +11812,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -129). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -11848,13 +11848,13 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.4358606557377049</v>
+        <v>0.4370168067226891</v>
       </c>
       <c r="G40" s="14" t="n">
         <v>129</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -11878,7 +11878,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 43.6% (fair +129). Your call.</t>
+          <t>Model 43.7% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -12046,13 +12046,13 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.5508352112676056</v>
+        <v>0.5501207547169812</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>-123</v>
+        <v>-122</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>-113</v>
+        <v>-112</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -12076,7 +12076,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 55.0% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -12112,10 +12112,10 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.4491943127962085</v>
+        <v>0.4498578199052132</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H44" s="15" t="n">
         <v>111</v>
@@ -12142,7 +12142,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 45.0% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -12178,13 +12178,13 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.5065517241379309</v>
+        <v>0.50895</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>-103</v>
+        <v>-104</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -12244,10 +12244,10 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.49345</v>
+        <v>0.49105</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H46" s="15" t="n">
         <v>100</v>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 49.1% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -12310,10 +12310,10 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.5085784313725491</v>
+        <v>0.5117156862745098</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>-103</v>
+        <v>-105</v>
       </c>
       <c r="H47" s="15" t="n">
         <v>104</v>
@@ -12340,7 +12340,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -103). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -12376,13 +12376,13 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.4914</v>
+        <v>0.4882671641791045</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-105</v>
+        <v>-101</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -12406,7 +12406,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -12580,7 +12580,7 @@
         <v>119</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -12970,13 +12970,13 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.4555299539170507</v>
+        <v>0.4547706422018349</v>
       </c>
       <c r="G57" s="14" t="n">
         <v>120</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -13000,7 +13000,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +120). Your call.</t>
+          <t>Model 45.5% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -13036,7 +13036,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5444543778801844</v>
+        <v>0.5452092165898618</v>
       </c>
       <c r="G58" s="14" t="n">
         <v>-120</v>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -120). Your call.</t>
+          <t>Model 54.5% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -13234,13 +13234,13 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.4242578125</v>
+        <v>0.4242585551330798</v>
       </c>
       <c r="G61" s="14" t="n">
         <v>136</v>
       </c>
       <c r="H61" s="15" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
@@ -13366,10 +13366,10 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>-201</v>
+        <v>-196</v>
       </c>
       <c r="H63" s="15" t="n"/>
       <c r="I63" s="13">
@@ -13394,7 +13394,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 66.8% (fair -201). Your call.</t>
+          <t>Model 66.2% (fair -196). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -13430,10 +13430,10 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.3322</v>
+        <v>0.3382</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="H64" s="15" t="n"/>
       <c r="I64" s="13">
@@ -13458,7 +13458,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 33.2% (fair +201). Your call.</t>
+          <t>Model 33.8% (fair +196). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -13494,10 +13494,10 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.3911</v>
+        <v>0.3893</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -13522,7 +13522,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 39.1% (fair +156). Your call.</t>
+          <t>Model 38.9% (fair +157). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -13558,10 +13558,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.6089</v>
+        <v>0.6107</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-156</v>
+        <v>-157</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -13586,7 +13586,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 60.9% (fair -156). Your call.</t>
+          <t>Model 61.1% (fair -157). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -13750,13 +13750,13 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.5913622119815668</v>
+        <v>0.5944477477477478</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>-145</v>
+        <v>-147</v>
       </c>
       <c r="H69" s="15" t="n">
-        <v>-117</v>
+        <v>-122</v>
       </c>
       <c r="I69" s="13">
         <f>IF($H$69="","",IF($H$69&lt;0,-$H$69/(-$H$69+100),100/($H$69+100)))</f>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 59.1% (fair -145). Your call.</t>
+          <t>Model 59.4% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -13816,10 +13816,10 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.4086486486486487</v>
+        <v>0.4055405405405406</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H70" s="15" t="n">
         <v>122</v>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 40.9% (fair +145). Your call.</t>
+          <t>Model 40.6% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -13882,10 +13882,10 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.421015625</v>
+        <v>0.4183984374999999</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H71" s="15" t="n">
         <v>156</v>
@@ -13912,7 +13912,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 42.1% (fair +138). Your call.</t>
+          <t>Model 41.8% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -13948,13 +13948,13 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.579028125</v>
+        <v>0.5815939163498098</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>-138</v>
+        <v>-139</v>
       </c>
       <c r="H72" s="15" t="n">
-        <v>-156</v>
+        <v>-163</v>
       </c>
       <c r="I72" s="13">
         <f>IF($H$72="","",IF($H$72&lt;0,-$H$72/(-$H$72+100),100/($H$72+100)))</f>
@@ -13978,7 +13978,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 57.9% (fair -138). Your call.</t>
+          <t>Model 58.2% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -14014,13 +14014,13 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.4866346153846154</v>
+        <v>0.4828169014084507</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -14044,7 +14044,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 48.3% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -14080,10 +14080,10 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.5133442396313364</v>
+        <v>0.517226267281106</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>-105</v>
+        <v>-107</v>
       </c>
       <c r="H74" s="15" t="n">
         <v>-117</v>
@@ -14110,7 +14110,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -14278,10 +14278,10 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.5831</v>
+        <v>0.485793991416309</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>-140</v>
+        <v>106</v>
       </c>
       <c r="H77" s="15" t="n">
         <v>133</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 58.3% (fair -140). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.4169</v>
+        <v>0.5142101321585903</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>140</v>
+        <v>-106</v>
       </c>
       <c r="H78" s="15" t="n">
-        <v>-122</v>
+        <v>-127</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -14374,7 +14374,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 41.7% (fair +140). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -14410,7 +14410,7 @@
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.49285</v>
+        <v>0.49325</v>
       </c>
       <c r="G79" s="14" t="n">
         <v>103</v>
@@ -14476,13 +14476,13 @@
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.5071326923076923</v>
+        <v>0.5067450980392156</v>
       </c>
       <c r="G80" s="14" t="n">
         <v>-103</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>-108</v>
+        <v>-104</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -14542,13 +14542,13 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.4600000000000001</v>
+        <v>0.4596313364055299</v>
       </c>
       <c r="G81" s="14" t="n">
+        <v>118</v>
+      </c>
+      <c r="H81" s="15" t="n">
         <v>117</v>
-      </c>
-      <c r="H81" s="15" t="n">
-        <v>122</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -14572,7 +14572,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +117). Your call.</t>
+          <t>Model 46.0% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -14608,13 +14608,13 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.5399873873873874</v>
+        <v>0.5403933920704846</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>-117</v>
+        <v>-118</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>-122</v>
+        <v>-127</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -14638,7 +14638,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -117). Your call.</t>
+          <t>Model 54.0% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -14674,10 +14674,10 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4555</v>
+        <v>0.4605</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H83" s="15" t="n">
         <v>163</v>
@@ -14704,7 +14704,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +120). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -14740,10 +14740,10 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5445</v>
+        <v>0.5395</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-120</v>
+        <v>-117</v>
       </c>
       <c r="H84" s="15" t="n">
         <v>-127</v>
@@ -14770,7 +14770,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -120). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -14806,10 +14806,10 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.4079087452471483</v>
+        <v>0.4073003802281369</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H85" s="15" t="n">
         <v>163</v>
@@ -14836,7 +14836,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 40.8% (fair +145). Your call.</t>
+          <t>Model 40.7% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -14872,10 +14872,10 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5920680608365019</v>
+        <v>0.5926878326996198</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-145</v>
+        <v>-146</v>
       </c>
       <c r="H86" s="15" t="n">
         <v>-163</v>
@@ -14902,7 +14902,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 59.2% (fair -145). Your call.</t>
+          <t>Model 59.3% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -14938,10 +14938,10 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.5477</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>-121</v>
+        <v>-120</v>
       </c>
       <c r="H87" s="15" t="n"/>
       <c r="I87" s="13">
@@ -14966,7 +14966,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 54.5% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -15002,10 +15002,10 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.4523</v>
+        <v>0.4551</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H88" s="15" t="n"/>
       <c r="I88" s="13">
@@ -15030,7 +15030,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 45.5% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -15066,13 +15066,13 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.5815475409836066</v>
+        <v>0.5842200000000001</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>-139</v>
+        <v>-141</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>-144</v>
+        <v>-150</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -15096,7 +15096,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -139). Your call.</t>
+          <t>Model 58.4% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -15132,10 +15132,10 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.4184234234234235</v>
+        <v>0.4158108108108109</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H90" s="15" t="n">
         <v>122</v>
@@ -15162,7 +15162,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 41.8% (fair +139). Your call.</t>
+          <t>Model 41.6% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -15198,13 +15198,13 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.5353153153153154</v>
+        <v>0.5352995391705069</v>
       </c>
       <c r="G91" s="14" t="n">
         <v>-115</v>
       </c>
       <c r="H91" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
@@ -15584,7 +15584,7 @@
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.363</v>
+        <v>0.3641</v>
       </c>
       <c r="G97" s="14" t="n">
         <v>175</v>
@@ -15612,7 +15612,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 36.3% (fair +175). Your call.</t>
+          <t>Model 36.4% (fair +175). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -15648,7 +15648,7 @@
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.637</v>
+        <v>0.6359</v>
       </c>
       <c r="G98" s="14" t="n">
         <v>-175</v>
@@ -15676,7 +15676,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 63.7% (fair -175). Your call.</t>
+          <t>Model 63.6% (fair -175). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>

--- a/data/output/workbook/2026-07-03.xlsx
+++ b/data/output/workbook/2026-07-03.xlsx
@@ -520,7 +520,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10506075"/>
+    <ext cx="10125075" cy="10763250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -550,7 +550,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10734675"/>
+    <ext cx="10125075" cy="10848975"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -953,7 +953,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03 06:49</t>
+          <t>2026-07-03 08:59</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2990,245 +2990,170 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="29" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
         <is>
           <t>New York Mets offense vs Atlanta Braves defense</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="30" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B68" s="30" t="inlineStr">
+      <c r="B69" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C68" s="30" t="inlineStr">
+      <c r="C69" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D68" s="30" t="inlineStr">
+      <c r="D69" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E68" s="30" t="inlineStr">
+      <c r="E69" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F68" s="30" t="inlineStr">
+      <c r="F69" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G68" s="30" t="inlineStr">
+      <c r="G69" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H68" s="30" t="inlineStr">
+      <c r="H69" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I68" s="30" t="inlineStr">
+      <c r="I69" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J68" s="30" t="inlineStr">
+      <c r="J69" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K68" s="30" t="inlineStr">
+      <c r="K69" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L68" s="30" t="inlineStr">
+      <c r="L69" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M68" s="30" t="inlineStr">
+      <c r="M69" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N68" s="30" t="inlineStr">
+      <c r="N69" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O68" s="30" t="inlineStr">
+      <c r="O69" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P68" s="30" t="inlineStr">
+      <c r="P69" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q68" s="30" t="inlineStr">
+      <c r="Q69" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>3.848</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>3.867</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H69" s="36" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="33" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>4.433</v>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>3.824</v>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>7.306</v>
+        <v>3.848</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.1</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>3.867</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H70" s="36" t="inlineStr">
+        <is>
+          <t>25th</t>
         </is>
       </c>
       <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J70" s="33" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>4.65</v>
       </c>
       <c r="O70" s="32" t="n">
-        <v>9.5</v>
+        <v>4.433</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>7.312</v>
+        <v>3.824</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>0.9389999999999999</v>
+        <v>7.306</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>2.25</v>
+        <v>6.5</v>
       </c>
       <c r="D71" s="32" t="inlineStr">
         <is>
@@ -3282,28 +3207,28 @@
         </is>
       </c>
       <c r="O71" s="32" t="n">
-        <v>1</v>
+        <v>9.5</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>1.062</v>
+        <v>7.312</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>8.407999999999999</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>9.25</v>
+        <v>2.25</v>
       </c>
       <c r="D72" s="32" t="inlineStr">
         <is>
@@ -3357,315 +3282,315 @@
         </is>
       </c>
       <c r="O72" s="32" t="n">
-        <v>8.667</v>
+        <v>1</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>8.561999999999999</v>
+        <v>1.062</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>8.407999999999999</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>8.667</v>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>8.561999999999999</v>
+      </c>
+      <c r="Q73" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B73" s="32" t="n">
+      <c r="B74" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="C73" s="32" t="n">
+      <c r="C74" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="D73" s="32" t="n">
+      <c r="D74" s="32" t="n">
         <v>0.55</v>
       </c>
-      <c r="E73" s="32" t="n">
+      <c r="E74" s="32" t="n">
         <v>0.133</v>
       </c>
-      <c r="F73" s="32" t="n">
+      <c r="F74" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G73" s="32" t="n">
+      <c r="G74" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H73" s="36" t="inlineStr">
+      <c r="H74" s="36" t="inlineStr">
         <is>
           <t>27th</t>
         </is>
       </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="36" t="inlineStr">
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="36" t="inlineStr">
         <is>
           <t>23rd</t>
         </is>
       </c>
-      <c r="K73" s="32" t="n">
+      <c r="K74" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="L73" s="32" t="n">
+      <c r="L74" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="M73" s="32" t="n">
+      <c r="M74" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="N73" s="32" t="n">
+      <c r="N74" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="O73" s="32" t="n">
+      <c r="O74" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="P73" s="32" t="n">
+      <c r="P74" s="32" t="n">
         <v>0.569</v>
       </c>
-      <c r="Q73" s="35" t="inlineStr">
+      <c r="Q74" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="29" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
         <is>
           <t>Atlanta Braves offense vs New York Mets defense</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="30" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B76" s="30" t="inlineStr">
+      <c r="B77" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C76" s="30" t="inlineStr">
+      <c r="C77" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D76" s="30" t="inlineStr">
+      <c r="D77" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E76" s="30" t="inlineStr">
+      <c r="E77" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F76" s="30" t="inlineStr">
+      <c r="F77" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G76" s="30" t="inlineStr">
+      <c r="G77" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H76" s="30" t="inlineStr">
+      <c r="H77" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I76" s="30" t="inlineStr">
+      <c r="I77" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J76" s="30" t="inlineStr">
+      <c r="J77" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K76" s="30" t="inlineStr">
+      <c r="K77" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L76" s="30" t="inlineStr">
+      <c r="L77" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M76" s="30" t="inlineStr">
+      <c r="M77" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N76" s="30" t="inlineStr">
+      <c r="N77" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O76" s="30" t="inlineStr">
+      <c r="O77" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P76" s="30" t="inlineStr">
+      <c r="P77" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q76" s="30" t="inlineStr">
+      <c r="Q77" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>4.797</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="H77" s="36" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="34" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>4.833</v>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>4.582</v>
-      </c>
-      <c r="Q77" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>8.958</v>
+        <v>4.797</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>8.167</v>
-      </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>3.8</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="H78" s="36" t="inlineStr">
+        <is>
+          <t>27th</t>
         </is>
       </c>
       <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>5.45</v>
       </c>
       <c r="O78" s="32" t="n">
-        <v>6</v>
+        <v>4.833</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>7.918</v>
+        <v>4.582</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>1.333</v>
+        <v>8.958</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>1.833</v>
+        <v>8.167</v>
       </c>
       <c r="D79" s="32" t="inlineStr">
         <is>
@@ -3719,28 +3644,28 @@
         </is>
       </c>
       <c r="O79" s="32" t="n">
-        <v>1.25</v>
+        <v>6</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>0.918</v>
+        <v>7.918</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>7.688</v>
+        <v>1.333</v>
       </c>
       <c r="C80" s="32" t="n">
-        <v>7.167</v>
+        <v>1.833</v>
       </c>
       <c r="D80" s="32" t="inlineStr">
         <is>
@@ -3794,75 +3719,150 @@
         </is>
       </c>
       <c r="O80" s="32" t="n">
-        <v>9.25</v>
+        <v>1.25</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>9.061</v>
+        <v>0.918</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="n">
+        <v>7.688</v>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>7.167</v>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="32" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="P81" s="32" t="n">
+        <v>9.061</v>
+      </c>
+      <c r="Q81" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B81" s="32" t="n">
+      <c r="B82" s="32" t="n">
         <v>0.597</v>
       </c>
-      <c r="C81" s="32" t="n">
+      <c r="C82" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="D81" s="32" t="n">
+      <c r="D82" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="E81" s="32" t="n">
+      <c r="E82" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="F81" s="32" t="n">
+      <c r="F82" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="G81" s="32" t="n">
+      <c r="G82" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="H81" s="34" t="inlineStr">
+      <c r="H82" s="34" t="inlineStr">
         <is>
           <t>1st</t>
         </is>
       </c>
-      <c r="I81" s="32" t="inlineStr">
+      <c r="I82" s="32" t="inlineStr">
         <is>
           <t>★★</t>
         </is>
       </c>
-      <c r="J81" s="33" t="inlineStr">
+      <c r="J82" s="33" t="inlineStr">
         <is>
           <t>11th</t>
         </is>
       </c>
-      <c r="K81" s="32" t="n">
+      <c r="K82" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="L81" s="32" t="n">
+      <c r="L82" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="M81" s="32" t="n">
+      <c r="M82" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="N81" s="32" t="n">
+      <c r="N82" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="O81" s="32" t="n">
+      <c r="O82" s="32" t="n">
         <v>0.633</v>
       </c>
-      <c r="P81" s="32" t="n">
+      <c r="P82" s="32" t="n">
         <v>0.52</v>
       </c>
-      <c r="Q81" s="35" t="inlineStr">
+      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -3881,7 +3881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3898,249 +3898,174 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="29" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>San Francisco Giants offense vs Colorado Rockies defense</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B69" s="30" t="inlineStr">
+      <c r="B70" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C69" s="30" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D69" s="30" t="inlineStr">
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E69" s="30" t="inlineStr">
+      <c r="E70" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F69" s="30" t="inlineStr">
+      <c r="F70" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G69" s="30" t="inlineStr">
+      <c r="G70" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H69" s="30" t="inlineStr">
+      <c r="H70" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I69" s="30" t="inlineStr">
+      <c r="I70" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J69" s="30" t="inlineStr">
+      <c r="J70" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K69" s="30" t="inlineStr">
+      <c r="K70" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L69" s="30" t="inlineStr">
+      <c r="L70" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M69" s="30" t="inlineStr">
+      <c r="M70" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N69" s="30" t="inlineStr">
+      <c r="N70" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O69" s="30" t="inlineStr">
+      <c r="O70" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P69" s="30" t="inlineStr">
+      <c r="P70" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q69" s="30" t="inlineStr">
+      <c r="Q70" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B70" s="32" t="n">
-        <v>4.128</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>4.833</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>3.867</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="H70" s="33" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J70" s="36" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>5.533</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>5.675</v>
-      </c>
-      <c r="Q70" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>9.239000000000001</v>
+        <v>4.128</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.833</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>3.867</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="H71" s="33" t="inlineStr">
+        <is>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J71" s="36" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>5.95</v>
       </c>
       <c r="O71" s="32" t="n">
-        <v>12.75</v>
+        <v>6.5</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>9.779999999999999</v>
+        <v>5.675</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>0.978</v>
+        <v>9.239000000000001</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>1.2</v>
+        <v>12.2</v>
       </c>
       <c r="D72" s="32" t="inlineStr">
         <is>
@@ -4194,28 +4119,28 @@
         </is>
       </c>
       <c r="O72" s="32" t="n">
-        <v>1.25</v>
+        <v>12.75</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>1.24</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>7.587</v>
+        <v>0.978</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>9</v>
+        <v>1.2</v>
       </c>
       <c r="D73" s="32" t="inlineStr">
         <is>
@@ -4269,319 +4194,319 @@
         </is>
       </c>
       <c r="O73" s="32" t="n">
-        <v>6.75</v>
+        <v>1.25</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>7.28</v>
+        <v>1.24</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="n">
+        <v>7.587</v>
+      </c>
+      <c r="C74" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="32" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="Q74" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B74" s="32" t="n">
+      <c r="B75" s="32" t="n">
         <v>0.352</v>
       </c>
-      <c r="C74" s="32" t="n">
+      <c r="C75" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="D74" s="32" t="n">
+      <c r="D75" s="32" t="n">
         <v>0.15</v>
       </c>
-      <c r="E74" s="32" t="n">
+      <c r="E75" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="F74" s="32" t="n">
+      <c r="F75" s="32" t="n">
         <v>0.1</v>
       </c>
-      <c r="G74" s="32" t="n">
+      <c r="G75" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H74" s="36" t="inlineStr">
+      <c r="H75" s="36" t="inlineStr">
         <is>
           <t>29th</t>
         </is>
       </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="36" t="inlineStr">
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="36" t="inlineStr">
         <is>
           <t>21st</t>
         </is>
       </c>
-      <c r="K74" s="32" t="n">
+      <c r="K75" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="L74" s="32" t="n">
+      <c r="L75" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="M74" s="32" t="n">
+      <c r="M75" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="N74" s="32" t="n">
+      <c r="N75" s="32" t="n">
         <v>0.85</v>
       </c>
-      <c r="O74" s="32" t="n">
+      <c r="O75" s="32" t="n">
         <v>0.633</v>
       </c>
-      <c r="P74" s="32" t="n">
+      <c r="P75" s="32" t="n">
         <v>0.697</v>
       </c>
-      <c r="Q74" s="35" t="inlineStr">
+      <c r="Q75" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="29" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>Colorado Rockies offense vs San Francisco Giants defense</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B77" s="30" t="inlineStr">
+      <c r="B78" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C77" s="30" t="inlineStr">
+      <c r="C78" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D77" s="30" t="inlineStr">
+      <c r="D78" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E77" s="30" t="inlineStr">
+      <c r="E78" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F77" s="30" t="inlineStr">
+      <c r="F78" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G77" s="30" t="inlineStr">
+      <c r="G78" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H77" s="30" t="inlineStr">
+      <c r="H78" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I77" s="30" t="inlineStr">
+      <c r="I78" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J77" s="30" t="inlineStr">
+      <c r="J78" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K77" s="30" t="inlineStr">
+      <c r="K78" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L77" s="30" t="inlineStr">
+      <c r="L78" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M77" s="30" t="inlineStr">
+      <c r="M78" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N77" s="30" t="inlineStr">
+      <c r="N78" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O77" s="30" t="inlineStr">
+      <c r="O78" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P77" s="30" t="inlineStr">
+      <c r="P78" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q77" s="30" t="inlineStr">
+      <c r="Q78" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B78" s="32" t="n">
-        <v>4.779</v>
-      </c>
-      <c r="C78" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H78" s="34" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J78" s="34" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>3.533</v>
-      </c>
-      <c r="N78" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O78" s="32" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="P78" s="32" t="n">
-        <v>4.846</v>
-      </c>
-      <c r="Q78" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>8.32</v>
+        <v>4.779</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="D79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="D79" s="32" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="E79" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F79" s="32" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G79" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H79" s="34" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J79" s="34" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L79" s="32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M79" s="32" t="n">
+        <v>3.533</v>
+      </c>
+      <c r="N79" s="32" t="n">
+        <v>4.2</v>
       </c>
       <c r="O79" s="32" t="n">
-        <v>13.4</v>
+        <v>4.867</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>8.651999999999999</v>
+        <v>4.846</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>0.92</v>
+        <v>8.32</v>
       </c>
       <c r="C80" s="32" t="n">
-        <v>1.75</v>
+        <v>11.5</v>
       </c>
       <c r="D80" s="32" t="inlineStr">
         <is>
@@ -4635,28 +4560,28 @@
         </is>
       </c>
       <c r="O80" s="32" t="n">
-        <v>1.2</v>
+        <v>13.4</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>0.978</v>
+        <v>8.651999999999999</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>8.92</v>
+        <v>0.92</v>
       </c>
       <c r="C81" s="32" t="n">
-        <v>9</v>
+        <v>1.75</v>
       </c>
       <c r="D81" s="32" t="inlineStr">
         <is>
@@ -4710,75 +4635,150 @@
         </is>
       </c>
       <c r="O81" s="32" t="n">
-        <v>7.4</v>
+        <v>1.2</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>8.173999999999999</v>
+        <v>0.978</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="C82" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="D82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="P82" s="32" t="n">
+        <v>8.173999999999999</v>
+      </c>
+      <c r="Q82" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B82" s="32" t="n">
+      <c r="B83" s="32" t="n">
         <v>0.474</v>
       </c>
-      <c r="C82" s="32" t="n">
+      <c r="C83" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="D82" s="32" t="n">
+      <c r="D83" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="E82" s="32" t="n">
+      <c r="E83" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="F82" s="32" t="n">
+      <c r="F83" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="G82" s="32" t="n">
+      <c r="G83" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="H82" s="34" t="inlineStr">
+      <c r="H83" s="34" t="inlineStr">
         <is>
           <t>9th</t>
         </is>
       </c>
-      <c r="I82" s="32" t="inlineStr">
+      <c r="I83" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J82" s="36" t="inlineStr">
+      <c r="J83" s="36" t="inlineStr">
         <is>
           <t>26th</t>
         </is>
       </c>
-      <c r="K82" s="32" t="n">
+      <c r="K83" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="L82" s="32" t="n">
+      <c r="L83" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="M82" s="32" t="n">
+      <c r="M83" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="N82" s="32" t="n">
+      <c r="N83" s="32" t="n">
         <v>0.55</v>
       </c>
-      <c r="O82" s="32" t="n">
+      <c r="O83" s="32" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="P82" s="32" t="n">
+      <c r="P83" s="32" t="n">
         <v>0.535</v>
       </c>
-      <c r="Q82" s="35" t="inlineStr">
+      <c r="Q83" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7747,10 +7747,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6928897338403042</v>
+        <v>0.6882889733840305</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-226</v>
+        <v>-221</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>163</v>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 69.3% (fair -226). Your call.</t>
+          <t>Model 68.8% (fair -221). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -7813,13 +7813,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.655551330798479</v>
+        <v>0.6510937499999999</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-190</v>
+        <v>-187</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -7843,7 +7843,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 65.6% (fair -190). Your call.</t>
+          <t>Model 65.1% (fair -187). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6174444444444445</v>
+        <v>0.6165555555555554</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>-161</v>
@@ -7945,10 +7945,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5988888888888888</v>
+        <v>0.5947407407407407</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-149</v>
+        <v>-147</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>170</v>
@@ -7975,7 +7975,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 59.9% (fair -149). Your call.</t>
+          <t>Model 59.5% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5757551020408164</v>
+        <v>0.57576</v>
       </c>
       <c r="G9" s="14" t="n">
         <v>-136</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8077,13 +8077,13 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6663156398104265</v>
+        <v>0.6662857142857143</v>
       </c>
       <c r="G10" s="14" t="n">
         <v>-200</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-111</v>
+        <v>-110</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8143,13 +8143,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4010958904109589</v>
+        <v>0.4052631578947368</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 40.1% (fair +149). Your call.</t>
+          <t>Model 40.5% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8209,10 +8209,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5352995391705069</v>
+        <v>0.5313824884792627</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-115</v>
+        <v>-113</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>117</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8322,12 +8322,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Athletics</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -8337,14 +8337,14 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Athletics -1.5</t>
+          <t>Chicago Cubs -1.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4242585551330798</v>
+        <v>0.4260456273764259</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>163</v>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 42.6% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8388,32 +8388,32 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Miami Marlins @ Athletics</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Athletics -1.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.3972661870503597</v>
+        <v>0.4242585551330798</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8437,7 +8437,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 39.7% (fair +152). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8454,32 +8454,32 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4732618025751073</v>
+        <v>0.5187677725118482</v>
       </c>
       <c r="G16" s="14" t="n">
+        <v>-108</v>
+      </c>
+      <c r="H16" s="15" t="n">
         <v>111</v>
-      </c>
-      <c r="H16" s="15" t="n">
-        <v>133</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8503,7 +8503,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +111). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8520,32 +8520,32 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Athletics</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5310294117647059</v>
+        <v>0.4758260869565218</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-113</v>
+        <v>110</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8581,17 +8581,17 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -8601,17 +8601,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5944477477477478</v>
+        <v>0.402962962962963</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-147</v>
+        <v>148</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-122</v>
+        <v>170</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 59.4% (fair -147). Your call.</t>
+          <t>Model 40.3% (fair +148). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -8652,32 +8652,32 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>Miami Marlins @ Athletics</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5724272300469483</v>
+        <v>0.5310294117647059</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-134</v>
+        <v>-113</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-113</v>
+        <v>104</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -8713,17 +8713,17 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4073003802281369</v>
+        <v>0.5695194312796208</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>146</v>
+        <v>-132</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>163</v>
+        <v>-111</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 40.7% (fair +146). Your call.</t>
+          <t>Model 57.0% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -8803,10 +8803,10 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4183984374999999</v>
+        <v>0.421015625</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>156</v>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 41.8% (fair +139). Your call.</t>
+          <t>Model 42.1% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -8845,37 +8845,37 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.53225</v>
+        <v>0.5907657657657658</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-114</v>
+        <v>-144</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>100</v>
+        <v>-122</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -8899,7 +8899,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 59.1% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -8911,37 +8911,37 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs -1.5</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.42496</v>
+        <v>0.4073003802281369</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -8965,7 +8965,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 42.5% (fair +135). Your call.</t>
+          <t>Model 40.7% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -8982,32 +8982,32 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Under 10</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.509326923076923</v>
+        <v>0.504691943127962</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-104</v>
+        <v>-102</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -9031,7 +9031,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9048,32 +9048,32 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>San Francisco Giants @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5117156862745098</v>
+        <v>0.4398319327731092</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-105</v>
+        <v>127</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 44.0% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -9114,32 +9114,32 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Colorado Rockies</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies +1.5</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5501207547169812</v>
+        <v>0.5130392156862745</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-122</v>
+        <v>-105</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-112</v>
+        <v>104</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -9163,7 +9163,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 55.0% (fair -122). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -9180,32 +9180,32 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Colorado Rockies</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>St. Louis Cardinals +1.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4370168067226891</v>
+        <v>0.5739632286995515</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>129</v>
+        <v>-135</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>138</v>
+        <v>-123</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -9229,7 +9229,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 57.4% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -9241,37 +9241,37 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5300941176470588</v>
+        <v>0.5704873873873874</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-113</v>
+        <v>-133</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-104</v>
+        <v>-122</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -9295,7 +9295,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 57.0% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -9312,12 +9312,12 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -9327,17 +9327,17 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins +1.5</t>
+          <t>Cleveland Guardians -1.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5519943925233645</v>
+        <v>0.3834444444444444</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-123</v>
+        <v>161</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-114</v>
+        <v>170</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -9361,7 +9361,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 38.3% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -9394,7 +9394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P98"/>
+  <dimension ref="A1:P96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9538,7 +9538,7 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4550691244239632</v>
+        <v>0.454331797235023</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>120</v>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 45.5% (fair +120). Your call.</t>
+          <t>Model 45.4% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -9604,7 +9604,7 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5449396313364054</v>
+        <v>0.5456405529953917</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>-120</v>
@@ -9634,7 +9634,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 54.5% (fair -120). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -9670,13 +9670,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.46775</v>
+        <v>0.4812039215686274</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -9700,7 +9700,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9736,13 +9736,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.53225</v>
+        <v>0.5187677725118482</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-114</v>
+        <v>-108</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9802,13 +9802,13 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.42496</v>
+        <v>0.4260456273764259</v>
       </c>
       <c r="G9" s="14" t="n">
         <v>135</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9832,7 +9832,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 42.5% (fair +135). Your call.</t>
+          <t>Model 42.6% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9868,13 +9868,13 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5750246696035243</v>
+        <v>0.5739632286995515</v>
       </c>
       <c r="G10" s="14" t="n">
         <v>-135</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-127</v>
+        <v>-123</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 57.5% (fair -135). Your call.</t>
+          <t>Model 57.4% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9934,13 +9934,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4732618025751073</v>
+        <v>0.4758260869565218</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +111). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -10000,13 +10000,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5267484978540773</v>
+        <v>0.5241879310344828</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-111</v>
+        <v>-110</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-133</v>
+        <v>-132</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -111). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -10066,10 +10066,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5300941176470588</v>
+        <v>0.5769</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-113</v>
+        <v>-136</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>-104</v>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -10132,13 +10132,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.46995</v>
+        <v>0.4231</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -10162,7 +10162,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 47.0% (fair +113). Your call.</t>
+          <t>Model 42.3% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -10264,13 +10264,13 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.6663156398104265</v>
+        <v>0.6662857142857143</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>-200</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-111</v>
+        <v>-110</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -10330,13 +10330,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.3972661870503597</v>
+        <v>0.402962962962963</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -10360,7 +10360,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 39.7% (fair +152). Your call.</t>
+          <t>Model 40.3% (fair +148). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -10396,13 +10396,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.6027131386861314</v>
+        <v>0.5970148148148148</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-152</v>
+        <v>-148</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-174</v>
+        <v>-170</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 60.3% (fair -152). Your call.</t>
+          <t>Model 59.7% (fair -148). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -10462,13 +10462,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4527</v>
+        <v>0.4952745098039216</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-102</v>
+        <v>-104</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -10492,7 +10492,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -10528,10 +10528,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5473</v>
+        <v>0.504691943127962</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-121</v>
+        <v>-102</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>111</v>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -10594,13 +10594,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.447981220657277</v>
+        <v>0.4452803738317758</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -10624,7 +10624,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 44.8% (fair +123). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -10660,13 +10660,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5519943925233645</v>
+        <v>0.5546986175115207</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-123</v>
+        <v>-125</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-114</v>
+        <v>-117</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -10690,7 +10690,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10726,13 +10726,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5724272300469483</v>
+        <v>0.5695194312796208</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-134</v>
+        <v>-132</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-113</v>
+        <v>-111</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10756,7 +10756,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 57.0% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10792,13 +10792,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4275829383886255</v>
+        <v>0.4304784688995215</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10822,7 +10822,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +134). Your call.</t>
+          <t>Model 43.0% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10930,7 +10930,7 @@
         <v>113</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10990,13 +10990,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4543859649122807</v>
+        <v>0.4599099099099099</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -11020,7 +11020,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 45.4% (fair +120). Your call.</t>
+          <t>Model 46.0% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -11056,13 +11056,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5456524229074891</v>
+        <v>0.5400555555555555</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-120</v>
+        <v>-117</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-127</v>
+        <v>-125</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -11086,7 +11086,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 54.0% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -11122,13 +11122,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5354</v>
+        <v>0.5374</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-115</v>
+        <v>-116</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -11152,7 +11152,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 53.7% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -11188,13 +11188,13 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.4646</v>
+        <v>0.4626</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -11254,13 +11254,13 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.3825475285171103</v>
+        <v>0.3834444444444444</v>
       </c>
       <c r="G31" s="14" t="n">
         <v>161</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -11320,7 +11320,7 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.6174444444444445</v>
+        <v>0.6165555555555554</v>
       </c>
       <c r="G32" s="14" t="n">
         <v>-161</v>
@@ -11386,13 +11386,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.509326923076923</v>
+        <v>0.5130392156862745</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>-104</v>
+        <v>-105</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -11416,7 +11416,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -11452,13 +11452,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.4906730769230769</v>
+        <v>0.4869310679611651</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-108</v>
+        <v>-106</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -11482,7 +11482,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -11518,13 +11518,13 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4016</v>
+        <v>0.4066</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -11548,7 +11548,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 40.2% (fair +149). Your call.</t>
+          <t>Model 40.7% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -11584,13 +11584,13 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5984</v>
+        <v>0.5933999999999999</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-149</v>
+        <v>-146</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -11614,7 +11614,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 59.8% (fair -149). Your call.</t>
+          <t>Model 59.3% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -11650,10 +11650,10 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.3071111111111111</v>
+        <v>0.3117037037037037</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H37" s="15" t="n">
         <v>170</v>
@@ -11680,7 +11680,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 30.7% (fair +226). Your call.</t>
+          <t>Model 31.2% (fair +221). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -11716,10 +11716,10 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.6928897338403042</v>
+        <v>0.6882889733840305</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-226</v>
+        <v>-221</v>
       </c>
       <c r="H38" s="15" t="n">
         <v>163</v>
@@ -11746,7 +11746,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 69.3% (fair -226). Your call.</t>
+          <t>Model 68.8% (fair -221). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -11782,13 +11782,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.5629573770491804</v>
+        <v>0.5601756302521008</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>-129</v>
+        <v>-127</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>-144</v>
+        <v>-138</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -11812,7 +11812,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 56.0% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -11848,10 +11848,10 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.4370168067226891</v>
+        <v>0.4398319327731092</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H40" s="15" t="n">
         <v>138</v>
@@ -11878,7 +11878,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 44.0% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -11914,10 +11914,10 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.48</v>
+        <v>0.5281</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>108</v>
+        <v>-112</v>
       </c>
       <c r="H41" s="15" t="n">
         <v>127</v>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -11980,13 +11980,13 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.52</v>
+        <v>0.4719</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-108</v>
+        <v>112</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -12010,7 +12010,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -12027,32 +12027,32 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Colorado Rockies</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>00:15</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies +1.5</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.5501207547169812</v>
+        <v>0.512070297029703</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>-122</v>
+        <v>-105</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>-112</v>
+        <v>-102</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -12076,7 +12076,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 55.0% (fair -122). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -12093,32 +12093,32 @@
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Colorado Rockies</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C44" s="20" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>00:15</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E44" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants -1.5</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.4498578199052132</v>
+        <v>0.48795</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -12142,7 +12142,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 45.0% (fair +122). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -12169,22 +12169,22 @@
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.50895</v>
+        <v>0.5877</v>
       </c>
       <c r="G45" s="14" t="n">
+        <v>-143</v>
+      </c>
+      <c r="H45" s="15" t="n">
         <v>-104</v>
-      </c>
-      <c r="H45" s="15" t="n">
-        <v>100</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 58.8% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -12235,22 +12235,22 @@
       </c>
       <c r="D46" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E46" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.49105</v>
+        <v>0.4123</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 41.2% (fair +143). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -12301,22 +12301,22 @@
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Houston Astros -1.5</t>
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.5117156862745098</v>
+        <v>0.3489122807017543</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>-105</v>
+        <v>187</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -12340,7 +12340,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 34.9% (fair +187). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -12367,22 +12367,22 @@
       </c>
       <c r="D48" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E48" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Tampa Bay Rays +1.5</t>
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.4882671641791045</v>
+        <v>0.6510937499999999</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>105</v>
+        <v>-187</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-101</v>
+        <v>156</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -12406,7 +12406,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 65.1% (fair -187). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -12423,32 +12423,32 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>01:38</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros -1.5</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.3444561403508772</v>
+        <v>0.456</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>190</v>
+        <v>119</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>185</v>
+        <v>122</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -12472,7 +12472,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 34.4% (fair +190). Your call.</t>
+          <t>Model 45.6% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -12489,32 +12489,32 @@
       </c>
       <c r="B50" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C50" s="20" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>01:38</t>
         </is>
       </c>
       <c r="D50" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E50" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays +1.5</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.655551330798479</v>
+        <v>0.544</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-190</v>
+        <v>-119</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>163</v>
+        <v>-104</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -12538,7 +12538,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 65.6% (fair -190). Your call.</t>
+          <t>Model 54.4% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -12565,22 +12565,22 @@
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.4566</v>
+        <v>0.4843</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -12604,7 +12604,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 45.7% (fair +119). Your call.</t>
+          <t>Model 48.4% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -12631,22 +12631,22 @@
       </c>
       <c r="D52" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E52" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.5434</v>
+        <v>0.5157</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-119</v>
+        <v>-106</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>-104</v>
+        <v>108</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -12670,7 +12670,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 54.3% (fair -119). Your call.</t>
+          <t>Model 51.6% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -12697,22 +12697,22 @@
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Los Angeles Angels -1.5</t>
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4762</v>
+        <v>0.4052631578947368</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>117</v>
+        <v>185</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -12736,7 +12736,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 40.5% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -12763,22 +12763,22 @@
       </c>
       <c r="D54" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E54" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Boston Red Sox +1.5</t>
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5947407407407407</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-110</v>
+        <v>-147</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -12802,7 +12802,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 59.5% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -12819,32 +12819,32 @@
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Los Angeles Angels</t>
+          <t>Miami Marlins @ Athletics</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>01:38</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels -1.5</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.4010958904109589</v>
+        <v>0.4568202764976959</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>149</v>
+        <v>119</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>192</v>
+        <v>117</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -12868,7 +12868,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 40.1% (fair +149). Your call.</t>
+          <t>Model 45.7% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -12885,32 +12885,32 @@
       </c>
       <c r="B56" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Los Angeles Angels</t>
+          <t>Miami Marlins @ Athletics</t>
         </is>
       </c>
       <c r="C56" s="20" t="inlineStr">
         <is>
-          <t>01:38</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D56" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E56" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox +1.5</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.5988888888888888</v>
+        <v>0.5431744186046512</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-149</v>
+        <v>-119</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>170</v>
+        <v>-115</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -12934,7 +12934,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 59.9% (fair -149). Your call.</t>
+          <t>Model 54.3% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -12961,22 +12961,22 @@
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Over 10.5</t>
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.4547706422018349</v>
+        <v>0.4689686274509803</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>118</v>
+        <v>-104</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -13000,7 +13000,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 45.5% (fair +120). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -13027,22 +13027,22 @@
       </c>
       <c r="D58" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E58" s="20" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5452092165898618</v>
+        <v>0.5310294117647059</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-120</v>
+        <v>-113</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>-117</v>
+        <v>104</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 54.5% (fair -120). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -13093,22 +13093,22 @@
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Over 10.5</t>
+          <t>Athletics -1.5</t>
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.4689686274509803</v>
+        <v>0.4242585551330798</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>-104</v>
+        <v>163</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -13132,7 +13132,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 46.9% (fair +113). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -13159,22 +13159,22 @@
       </c>
       <c r="D60" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E60" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Miami Marlins +1.5</t>
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.5310294117647059</v>
+        <v>0.57576</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>-113</v>
+        <v>-136</v>
       </c>
       <c r="H60" s="15" t="n">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
@@ -13198,7 +13198,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -13215,33 +13215,31 @@
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Athletics</t>
+          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Athletics -1.5</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.4242585551330798</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>136</v>
-      </c>
-      <c r="H61" s="15" t="n">
-        <v>163</v>
-      </c>
+        <v>-196</v>
+      </c>
+      <c r="H61" s="15" t="n"/>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
         <v/>
@@ -13264,7 +13262,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 66.2% (fair -196). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -13281,33 +13279,31 @@
       </c>
       <c r="B62" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Athletics</t>
+          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="C62" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins +1.5</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.5757551020408164</v>
+        <v>0.3382</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-136</v>
-      </c>
-      <c r="H62" s="15" t="n">
-        <v>145</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="H62" s="15" t="n"/>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
         <v/>
@@ -13330,7 +13326,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 33.8% (fair +196). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -13347,12 +13343,12 @@
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
@@ -13362,14 +13358,14 @@
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.3931</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>-196</v>
+        <v>154</v>
       </c>
       <c r="H63" s="15" t="n"/>
       <c r="I63" s="13">
@@ -13394,7 +13390,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 66.2% (fair -196). Your call.</t>
+          <t>Model 39.3% (fair +154). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -13411,12 +13407,12 @@
       </c>
       <c r="B64" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C64" s="20" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr">
@@ -13426,14 +13422,14 @@
       </c>
       <c r="E64" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.3382</v>
+        <v>0.6069</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>196</v>
+        <v>-154</v>
       </c>
       <c r="H64" s="15" t="n"/>
       <c r="I64" s="13">
@@ -13458,7 +13454,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 33.8% (fair +196). Your call.</t>
+          <t>Model 60.7% (fair -154). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -13475,7 +13471,7 @@
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
@@ -13490,14 +13486,14 @@
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.3893</v>
+        <v>0.5416</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>157</v>
+        <v>-118</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -13522,7 +13518,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 38.9% (fair +157). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -13539,7 +13535,7 @@
       </c>
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C66" s="20" t="inlineStr">
@@ -13554,14 +13550,14 @@
       </c>
       <c r="E66" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.6107</v>
+        <v>0.4583</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-157</v>
+        <v>118</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -13586,7 +13582,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 61.1% (fair -157). Your call.</t>
+          <t>Model 45.8% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -13598,17 +13594,17 @@
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ Seattle Mariners</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
@@ -13618,16 +13614,18 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.5423</v>
+        <v>0.5907657657657658</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>-118</v>
-      </c>
-      <c r="H67" s="15" t="n"/>
+        <v>-144</v>
+      </c>
+      <c r="H67" s="15" t="n">
+        <v>-122</v>
+      </c>
       <c r="I67" s="13">
         <f>IF($H$67="","",IF($H$67&lt;0,-$H$67/(-$H$67+100),100/($H$67+100)))</f>
         <v/>
@@ -13650,7 +13648,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -118). Your call.</t>
+          <t>Model 59.1% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -13662,17 +13660,17 @@
     <row r="68">
       <c r="A68" s="20" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B68" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ Seattle Mariners</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C68" s="20" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="D68" s="20" t="inlineStr">
@@ -13682,16 +13680,18 @@
       </c>
       <c r="E68" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.4577</v>
+        <v>0.4092165898617512</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>118</v>
-      </c>
-      <c r="H68" s="15" t="n"/>
+        <v>144</v>
+      </c>
+      <c r="H68" s="15" t="n">
+        <v>117</v>
+      </c>
       <c r="I68" s="13">
         <f>IF($H$68="","",IF($H$68&lt;0,-$H$68/(-$H$68+100),100/($H$68+100)))</f>
         <v/>
@@ -13714,7 +13714,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 45.8% (fair +118). Your call.</t>
+          <t>Model 40.9% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -13731,12 +13731,12 @@
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
@@ -13746,17 +13746,17 @@
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.5944477477477478</v>
+        <v>0.421015625</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>-147</v>
+        <v>138</v>
       </c>
       <c r="H69" s="15" t="n">
-        <v>-122</v>
+        <v>156</v>
       </c>
       <c r="I69" s="13">
         <f>IF($H$69="","",IF($H$69&lt;0,-$H$69/(-$H$69+100),100/($H$69+100)))</f>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 59.4% (fair -147). Your call.</t>
+          <t>Model 42.1% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -13797,12 +13797,12 @@
       </c>
       <c r="B70" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C70" s="20" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D70" s="20" t="inlineStr">
@@ -13812,17 +13812,17 @@
       </c>
       <c r="E70" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.4055405405405406</v>
+        <v>0.579028125</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>147</v>
+        <v>-138</v>
       </c>
       <c r="H70" s="15" t="n">
-        <v>122</v>
+        <v>-156</v>
       </c>
       <c r="I70" s="13">
         <f>IF($H$70="","",IF($H$70&lt;0,-$H$70/(-$H$70+100),100/($H$70+100)))</f>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 40.6% (fair +147). Your call.</t>
+          <t>Model 57.9% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -13863,12 +13863,12 @@
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
@@ -13878,17 +13878,17 @@
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.4183984374999999</v>
+        <v>0.4828169014084507</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="H71" s="15" t="n">
-        <v>156</v>
+        <v>113</v>
       </c>
       <c r="I71" s="13">
         <f>IF($H$71="","",IF($H$71&lt;0,-$H$71/(-$H$71+100),100/($H$71+100)))</f>
@@ -13912,7 +13912,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 41.8% (fair +139). Your call.</t>
+          <t>Model 48.3% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -13929,12 +13929,12 @@
       </c>
       <c r="B72" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C72" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D72" s="20" t="inlineStr">
@@ -13944,17 +13944,17 @@
       </c>
       <c r="E72" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5815939163498098</v>
+        <v>0.517226267281106</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>-139</v>
+        <v>-107</v>
       </c>
       <c r="H72" s="15" t="n">
-        <v>-163</v>
+        <v>-117</v>
       </c>
       <c r="I72" s="13">
         <f>IF($H$72="","",IF($H$72&lt;0,-$H$72/(-$H$72+100),100/($H$72+100)))</f>
@@ -13978,7 +13978,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -139). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -13995,12 +13995,12 @@
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
@@ -14010,17 +14010,17 @@
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.4828169014084507</v>
+        <v>0.419327731092437</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -14044,7 +14044,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 48.3% (fair +107). Your call.</t>
+          <t>Model 41.9% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -14061,12 +14061,12 @@
       </c>
       <c r="B74" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C74" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
@@ -14076,17 +14076,17 @@
       </c>
       <c r="E74" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.517226267281106</v>
+        <v>0.5806436974789916</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>-107</v>
+        <v>-138</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>-117</v>
+        <v>-138</v>
       </c>
       <c r="I74" s="13">
         <f>IF($H$74="","",IF($H$74&lt;0,-$H$74/(-$H$74+100),100/($H$74+100)))</f>
@@ -14110,7 +14110,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 58.1% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -14127,12 +14127,12 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ Seattle Mariners</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
@@ -14142,17 +14142,17 @@
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.419327731092437</v>
+        <v>0.485793991416309</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -14176,7 +14176,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 41.9% (fair +138). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -14193,12 +14193,12 @@
       </c>
       <c r="B76" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ Seattle Mariners</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C76" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
@@ -14208,17 +14208,17 @@
       </c>
       <c r="E76" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.5806436974789916</v>
+        <v>0.5142101321585903</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-138</v>
+        <v>-106</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>-138</v>
+        <v>-127</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -14242,7 +14242,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 58.1% (fair -138). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -14259,7 +14259,7 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
@@ -14274,17 +14274,17 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.485793991416309</v>
+        <v>0.49325</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -14325,7 +14325,7 @@
       </c>
       <c r="B78" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C78" s="20" t="inlineStr">
@@ -14340,17 +14340,17 @@
       </c>
       <c r="E78" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5142101321585903</v>
+        <v>0.5067450980392156</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-106</v>
+        <v>-103</v>
       </c>
       <c r="H78" s="15" t="n">
-        <v>-127</v>
+        <v>-104</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -14374,7 +14374,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
@@ -14406,17 +14406,17 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.49325</v>
+        <v>0.4624884792626728</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -14440,7 +14440,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 46.2% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -14457,7 +14457,7 @@
       </c>
       <c r="B80" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C80" s="20" t="inlineStr">
@@ -14472,17 +14472,17 @@
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.5067450980392156</v>
+        <v>0.5375144144144144</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>-103</v>
+        <v>-116</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>-104</v>
+        <v>-122</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -14506,7 +14506,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -14523,12 +14523,12 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
@@ -14538,17 +14538,17 @@
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.4596313364055299</v>
+        <v>0.4605</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>117</v>
+        <v>163</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -14572,7 +14572,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +118). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -14589,12 +14589,12 @@
       </c>
       <c r="B82" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C82" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
@@ -14604,14 +14604,14 @@
       </c>
       <c r="E82" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.5403933920704846</v>
+        <v>0.5395</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>-118</v>
+        <v>-117</v>
       </c>
       <c r="H82" s="15" t="n">
         <v>-127</v>
@@ -14638,7 +14638,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -118). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -14655,7 +14655,7 @@
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
@@ -14670,14 +14670,14 @@
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4605</v>
+        <v>0.4073003802281369</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="H83" s="15" t="n">
         <v>163</v>
@@ -14704,7 +14704,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 40.7% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="B84" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C84" s="20" t="inlineStr">
@@ -14736,17 +14736,17 @@
       </c>
       <c r="E84" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5395</v>
+        <v>0.5926878326996198</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-117</v>
+        <v>-146</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>-127</v>
+        <v>-163</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -14770,7 +14770,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 59.3% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -14787,12 +14787,12 @@
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>San Francisco Giants @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
@@ -14802,18 +14802,16 @@
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.4073003802281369</v>
+        <v>0.5487</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>146</v>
-      </c>
-      <c r="H85" s="15" t="n">
-        <v>163</v>
-      </c>
+        <v>-122</v>
+      </c>
+      <c r="H85" s="15" t="n"/>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
         <v/>
@@ -14836,7 +14834,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 40.7% (fair +146). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -14853,12 +14851,12 @@
       </c>
       <c r="B86" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>San Francisco Giants @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C86" s="20" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D86" s="20" t="inlineStr">
@@ -14868,18 +14866,16 @@
       </c>
       <c r="E86" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5926878326996198</v>
+        <v>0.4513</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-146</v>
-      </c>
-      <c r="H86" s="15" t="n">
-        <v>-163</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="H86" s="15" t="n"/>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
         <v/>
@@ -14902,7 +14898,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 59.3% (fair -146). Your call.</t>
+          <t>Model 45.1% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -14919,7 +14915,7 @@
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Colorado Rockies</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
@@ -14934,16 +14930,18 @@
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.5449000000000001</v>
+        <v>0.5704873873873874</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>-120</v>
-      </c>
-      <c r="H87" s="15" t="n"/>
+        <v>-133</v>
+      </c>
+      <c r="H87" s="15" t="n">
+        <v>-122</v>
+      </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
         <v/>
@@ -14966,7 +14964,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 54.5% (fair -120). Your call.</t>
+          <t>Model 57.0% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -14983,7 +14981,7 @@
       </c>
       <c r="B88" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Colorado Rockies</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C88" s="20" t="inlineStr">
@@ -14998,16 +14996,18 @@
       </c>
       <c r="E88" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.4551</v>
+        <v>0.4295045045045046</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>120</v>
-      </c>
-      <c r="H88" s="15" t="n"/>
+        <v>133</v>
+      </c>
+      <c r="H88" s="15" t="n">
+        <v>122</v>
+      </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
         <v/>
@@ -15030,7 +15030,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 45.5% (fair +120). Your call.</t>
+          <t>Model 43.0% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -15047,12 +15047,12 @@
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Kansas City Royals</t>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>01:38</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
@@ -15062,17 +15062,17 @@
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.5842200000000001</v>
+        <v>0.5313824884792627</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>-141</v>
+        <v>-113</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>-150</v>
+        <v>117</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -15096,7 +15096,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -141). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -15113,12 +15113,12 @@
       </c>
       <c r="B90" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Kansas City Royals</t>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C90" s="20" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>01:38</t>
         </is>
       </c>
       <c r="D90" s="20" t="inlineStr">
@@ -15128,18 +15128,16 @@
       </c>
       <c r="E90" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.4158108108108109</v>
+        <v>0.4686</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>140</v>
-      </c>
-      <c r="H90" s="15" t="n">
-        <v>122</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="H90" s="15" t="n"/>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
         <v/>
@@ -15162,7 +15160,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +140). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -15179,12 +15177,12 @@
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Los Angeles Angels</t>
+          <t>Miami Marlins @ Athletics</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>01:38</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
@@ -15194,18 +15192,16 @@
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.5352995391705069</v>
+        <v>0.5261</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>-115</v>
-      </c>
-      <c r="H91" s="15" t="n">
-        <v>117</v>
-      </c>
+        <v>-111</v>
+      </c>
+      <c r="H91" s="15" t="n"/>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
         <v/>
@@ -15228,7 +15224,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -15245,12 +15241,12 @@
       </c>
       <c r="B92" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Los Angeles Angels</t>
+          <t>Miami Marlins @ Athletics</t>
         </is>
       </c>
       <c r="C92" s="20" t="inlineStr">
         <is>
-          <t>01:38</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D92" s="20" t="inlineStr">
@@ -15260,14 +15256,14 @@
       </c>
       <c r="E92" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.4647</v>
+        <v>0.4739</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H92" s="15" t="n"/>
       <c r="I92" s="13">
@@ -15292,7 +15288,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -15309,7 +15305,7 @@
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Athletics</t>
+          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
@@ -15324,14 +15320,14 @@
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.5261</v>
+        <v>0.6854</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>-111</v>
+        <v>-218</v>
       </c>
       <c r="H93" s="15" t="n"/>
       <c r="I93" s="13">
@@ -15356,7 +15352,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 68.5% (fair -218). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -15373,7 +15369,7 @@
       </c>
       <c r="B94" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Athletics</t>
+          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="C94" s="20" t="inlineStr">
@@ -15388,14 +15384,14 @@
       </c>
       <c r="E94" s="20" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.4739</v>
+        <v>0.3146</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>111</v>
+        <v>218</v>
       </c>
       <c r="H94" s="15" t="n"/>
       <c r="I94" s="13">
@@ -15420,7 +15416,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 31.5% (fair +218). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -15437,12 +15433,12 @@
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
@@ -15452,14 +15448,14 @@
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.6854</v>
+        <v>0.3641</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>-218</v>
+        <v>175</v>
       </c>
       <c r="H95" s="15" t="n"/>
       <c r="I95" s="13">
@@ -15484,7 +15480,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 68.5% (fair -218). Your call.</t>
+          <t>Model 36.4% (fair +175). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -15501,12 +15497,12 @@
       </c>
       <c r="B96" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C96" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D96" s="20" t="inlineStr">
@@ -15516,14 +15512,14 @@
       </c>
       <c r="E96" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.3146</v>
+        <v>0.6359</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>218</v>
+        <v>-175</v>
       </c>
       <c r="H96" s="15" t="n"/>
       <c r="I96" s="13">
@@ -15548,7 +15544,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 31.5% (fair +218). Your call.</t>
+          <t>Model 63.6% (fair -175). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -15557,137 +15553,9 @@
         <v/>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="B97" s="12" t="inlineStr">
-        <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
-        </is>
-      </c>
-      <c r="C97" s="12" t="inlineStr">
-        <is>
-          <t>02:10</t>
-        </is>
-      </c>
-      <c r="D97" s="12" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E97" s="12" t="inlineStr">
-        <is>
-          <t>San Diego Padres</t>
-        </is>
-      </c>
-      <c r="F97" s="13" t="n">
-        <v>0.3641</v>
-      </c>
-      <c r="G97" s="14" t="n">
-        <v>175</v>
-      </c>
-      <c r="H97" s="15" t="n"/>
-      <c r="I97" s="13">
-        <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
-        <v/>
-      </c>
-      <c r="J97" s="16">
-        <f>IF($H$97="","",$F$97*IF($H$97&lt;0,-100/$H$97,$H$97/100)-(1-$F$97))</f>
-        <v/>
-      </c>
-      <c r="K97" s="17">
-        <f>IF($H$97="","",MAX(0,($F$97*IF($H$97&lt;0,-100/$H$97,$H$97/100)-(1-$F$97))/IF($H$97&lt;0,-100/$H$97,$H$97/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L97" s="18">
-        <f>IF($H$97="","",ROUND(MIN($K$97,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M97" s="12">
-        <f>IF($J$97="","",IF($J$97&lt;0,"Pass",IF($J$97&lt;'Settings'!$B$4,"Thin",IF($J$97&lt;0.06,"✅ Sharp band",IF($J$97&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N97" s="19" t="inlineStr">
-        <is>
-          <t>Model 36.4% (fair +175). Your call.</t>
-        </is>
-      </c>
-      <c r="O97" s="15" t="n"/>
-      <c r="P97" s="16">
-        <f>IF(OR($H$97="",$O$97=""),"",(1+IF($H$97&lt;0,-100/$H$97,$H$97/100))/(1+IF($O$97&lt;0,-100/$O$97,$O$97/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="B98" s="20" t="inlineStr">
-        <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
-        </is>
-      </c>
-      <c r="C98" s="20" t="inlineStr">
-        <is>
-          <t>02:10</t>
-        </is>
-      </c>
-      <c r="D98" s="20" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E98" s="20" t="inlineStr">
-        <is>
-          <t>Los Angeles Dodgers</t>
-        </is>
-      </c>
-      <c r="F98" s="13" t="n">
-        <v>0.6359</v>
-      </c>
-      <c r="G98" s="14" t="n">
-        <v>-175</v>
-      </c>
-      <c r="H98" s="15" t="n"/>
-      <c r="I98" s="13">
-        <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
-        <v/>
-      </c>
-      <c r="J98" s="16">
-        <f>IF($H$98="","",$F$98*IF($H$98&lt;0,-100/$H$98,$H$98/100)-(1-$F$98))</f>
-        <v/>
-      </c>
-      <c r="K98" s="17">
-        <f>IF($H$98="","",MAX(0,($F$98*IF($H$98&lt;0,-100/$H$98,$H$98/100)-(1-$F$98))/IF($H$98&lt;0,-100/$H$98,$H$98/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L98" s="18">
-        <f>IF($H$98="","",ROUND(MIN($K$98,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M98" s="12">
-        <f>IF($J$98="","",IF($J$98&lt;0,"Pass",IF($J$98&lt;'Settings'!$B$4,"Thin",IF($J$98&lt;0.06,"✅ Sharp band",IF($J$98&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N98" s="19" t="inlineStr">
-        <is>
-          <t>Model 63.6% (fair -175). Your call.</t>
-        </is>
-      </c>
-      <c r="O98" s="15" t="n"/>
-      <c r="P98" s="16">
-        <f>IF(OR($H$98="",$O$98=""),"",(1+IF($H$98&lt;0,-100/$H$98,$H$98/100))/(1+IF($O$98&lt;0,-100/$O$98,$O$98/100))-1)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J98">
+  <conditionalFormatting sqref="J5:J96">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>

--- a/data/output/workbook/2026-07-03.xlsx
+++ b/data/output/workbook/2026-07-03.xlsx
@@ -370,7 +370,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10544175"/>
+    <ext cx="10125075" cy="10801350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -490,7 +490,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10763250"/>
+    <ext cx="10125075" cy="10506075"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -550,7 +550,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10848975"/>
+    <ext cx="10125075" cy="10582275"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -580,7 +580,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10163175"/>
+    <ext cx="10125075" cy="10544175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -610,7 +610,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9801225"/>
+    <ext cx="10125075" cy="10429875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -953,7 +953,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03 17:05</t>
+          <t>2026-07-03 18:15</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2082,174 +2082,249 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Chicago White Sox offense vs Cleveland Guardians defense</t>
+        </is>
+      </c>
+    </row>
     <row r="68">
-      <c r="A68" s="29" t="inlineStr">
-        <is>
-          <t>Chicago White Sox offense vs Cleveland Guardians defense</t>
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B69" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C69" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D69" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E69" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F69" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G69" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H69" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I69" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J69" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K69" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L69" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M69" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N69" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O69" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P69" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q69" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H69" s="33" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J69" s="33" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>4.367</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>4.141</v>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>4.933</v>
+        <v>7.792</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>5.333</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H70" s="33" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J70" s="33" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>4.267</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>4</v>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O70" s="32" t="n">
-        <v>4.367</v>
+        <v>10.5</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>4.141</v>
+        <v>7.939</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>7.792</v>
+        <v>1.354</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>8.800000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="D71" s="32" t="inlineStr">
         <is>
@@ -2303,28 +2378,28 @@
         </is>
       </c>
       <c r="O71" s="32" t="n">
-        <v>10.5</v>
+        <v>0.75</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>7.939</v>
+        <v>1.143</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>1.354</v>
+        <v>9.208</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>1.6</v>
+        <v>7.8</v>
       </c>
       <c r="D72" s="32" t="inlineStr">
         <is>
@@ -2378,315 +2453,315 @@
         </is>
       </c>
       <c r="O72" s="32" t="n">
-        <v>0.75</v>
+        <v>9.5</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>1.143</v>
+        <v>9.388</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>9.208</v>
+        <v>0.589</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.6</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>7th</t>
         </is>
       </c>
       <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="34" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>0.3</v>
       </c>
       <c r="O73" s="32" t="n">
-        <v>9.5</v>
+        <v>0.367</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>9.388</v>
+        <v>0.36</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>0.589</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D74" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E74" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F74" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G74" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="N74" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="Q74" s="35" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians offense vs Chicago White Sox defense</t>
+        </is>
+      </c>
+    </row>
     <row r="76">
-      <c r="A76" s="29" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians offense vs Chicago White Sox defense</t>
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B77" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C77" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D77" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E77" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F77" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G77" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H77" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I77" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J77" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K77" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L77" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M77" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N77" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O77" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P77" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q77" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>3.949</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H77" s="33" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr"/>
+      <c r="J77" s="33" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>3.867</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O77" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P77" s="32" t="n">
+        <v>4.733</v>
+      </c>
+      <c r="Q77" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>3.949</v>
+        <v>7.735</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H78" s="33" t="inlineStr">
-        <is>
-          <t>13th</t>
+        <v>9.75</v>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="33" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>3.867</v>
-      </c>
-      <c r="N78" s="32" t="n">
-        <v>4.2</v>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O78" s="32" t="n">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>4.733</v>
+        <v>7.854</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>7.735</v>
+        <v>0.959</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>9.75</v>
+        <v>0.25</v>
       </c>
       <c r="D79" s="32" t="inlineStr">
         <is>
@@ -2740,28 +2815,28 @@
         </is>
       </c>
       <c r="O79" s="32" t="n">
-        <v>7</v>
+        <v>0.6</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>7.854</v>
+        <v>1.062</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>0.959</v>
+        <v>8</v>
       </c>
       <c r="C80" s="32" t="n">
-        <v>0.25</v>
+        <v>11.25</v>
       </c>
       <c r="D80" s="32" t="inlineStr">
         <is>
@@ -2815,146 +2890,71 @@
         </is>
       </c>
       <c r="O80" s="32" t="n">
-        <v>0.6</v>
+        <v>7.2</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>1.062</v>
+        <v>7.938</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>8</v>
+        <v>0.507</v>
       </c>
       <c r="C81" s="32" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.367</v>
+      </c>
+      <c r="D81" s="32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E81" s="32" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="F81" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G81" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H81" s="33" t="inlineStr">
+        <is>
+          <t>18th</t>
         </is>
       </c>
       <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J81" s="33" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L81" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M81" s="32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="N81" s="32" t="n">
+        <v>0.55</v>
       </c>
       <c r="O81" s="32" t="n">
-        <v>7.2</v>
+        <v>0.533</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>7.938</v>
+        <v>0.548</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="C82" s="32" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="D82" s="32" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E82" s="32" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="F82" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G82" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H82" s="33" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="33" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L82" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M82" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="N82" s="32" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="O82" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>0.548</v>
-      </c>
-      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -3881,7 +3881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3898,174 +3898,324 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>San Francisco Giants offense vs Colorado Rockies defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>San Francisco Giants offense vs Colorado Rockies defense</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>4.128</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>4.833</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>3.867</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="H69" s="33" t="inlineStr">
+        <is>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J69" s="36" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>5.675</v>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>9.239000000000001</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="Q70" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>4.128</v>
+        <v>0.978</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>4.833</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>3.867</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="H71" s="33" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J71" s="36" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>5.533</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>5.95</v>
+        <v>1.2</v>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O71" s="32" t="n">
-        <v>6.5</v>
+        <v>1.25</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>5.675</v>
+        <v>1.24</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>9.239000000000001</v>
+        <v>7.587</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>12.2</v>
+        <v>9</v>
       </c>
       <c r="D72" s="32" t="inlineStr">
         <is>
@@ -4119,394 +4269,394 @@
         </is>
       </c>
       <c r="O72" s="32" t="n">
-        <v>12.75</v>
+        <v>6.75</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>9.779999999999999</v>
+        <v>7.28</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>0.978</v>
+        <v>0.352</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.333</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="36" t="inlineStr">
+        <is>
+          <t>29th</t>
         </is>
       </c>
       <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="36" t="inlineStr">
+        <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>0.85</v>
       </c>
       <c r="O73" s="32" t="n">
-        <v>1.25</v>
+        <v>0.633</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>1.24</v>
+        <v>0.697</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>7.587</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="D74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="Q74" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>0.352</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="36" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="36" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>0.697</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>Colorado Rockies offense vs San Francisco Giants defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>Colorado Rockies offense vs San Francisco Giants defense</t>
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>4.779</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H77" s="34" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J77" s="34" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>3.533</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O77" s="32" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="P77" s="32" t="n">
+        <v>4.846</v>
+      </c>
+      <c r="Q77" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A78" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="32" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>8.651999999999999</v>
+      </c>
+      <c r="Q78" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>4.779</v>
+        <v>0.92</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="D79" s="32" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="E79" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="F79" s="32" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="G79" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="I79" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L79" s="32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M79" s="32" t="n">
-        <v>3.533</v>
-      </c>
-      <c r="N79" s="32" t="n">
-        <v>4.2</v>
+        <v>1.75</v>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr"/>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O79" s="32" t="n">
-        <v>4.867</v>
+        <v>1.2</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>4.846</v>
+        <v>0.978</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>8.32</v>
+        <v>8.92</v>
       </c>
       <c r="C80" s="32" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="D80" s="32" t="inlineStr">
         <is>
@@ -4560,225 +4710,75 @@
         </is>
       </c>
       <c r="O80" s="32" t="n">
-        <v>13.4</v>
+        <v>7.4</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>8.651999999999999</v>
+        <v>8.173999999999999</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>0.92</v>
+        <v>0.474</v>
       </c>
       <c r="C81" s="32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.533</v>
+      </c>
+      <c r="D81" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E81" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F81" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G81" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H81" s="34" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J81" s="36" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L81" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M81" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="N81" s="32" t="n">
+        <v>0.55</v>
       </c>
       <c r="O81" s="32" t="n">
-        <v>1.2</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>0.978</v>
+        <v>0.535</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="n">
-        <v>8.92</v>
-      </c>
-      <c r="C82" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="D82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O82" s="32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>8.173999999999999</v>
-      </c>
-      <c r="Q82" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="32" t="n">
-        <v>0.474</v>
-      </c>
-      <c r="C83" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="D83" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E83" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F83" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G83" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H83" s="34" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="I83" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J83" s="36" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K83" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L83" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M83" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="N83" s="32" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="O83" s="32" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="P83" s="32" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="Q83" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -4797,7 +4797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4814,324 +4814,174 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="29" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
         <is>
           <t>Tampa Bay Rays offense vs Houston Astros defense</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="30" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B66" s="30" t="inlineStr">
+      <c r="B68" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C66" s="30" t="inlineStr">
+      <c r="C68" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D66" s="30" t="inlineStr">
+      <c r="D68" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E66" s="30" t="inlineStr">
+      <c r="E68" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F66" s="30" t="inlineStr">
+      <c r="F68" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G66" s="30" t="inlineStr">
+      <c r="G68" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H66" s="30" t="inlineStr">
+      <c r="H68" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I66" s="30" t="inlineStr">
+      <c r="I68" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J66" s="30" t="inlineStr">
+      <c r="J68" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K66" s="30" t="inlineStr">
+      <c r="K68" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L66" s="30" t="inlineStr">
+      <c r="L68" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M66" s="30" t="inlineStr">
+      <c r="M68" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N66" s="30" t="inlineStr">
+      <c r="N68" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O66" s="30" t="inlineStr">
+      <c r="O68" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P66" s="30" t="inlineStr">
+      <c r="P68" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q66" s="30" t="inlineStr">
+      <c r="Q68" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B67" s="32" t="n">
-        <v>4.712</v>
-      </c>
-      <c r="C67" s="32" t="n">
-        <v>4.367</v>
-      </c>
-      <c r="D67" s="32" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="E67" s="32" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="F67" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="G67" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H67" s="34" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="I67" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J67" s="36" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="K67" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L67" s="32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M67" s="32" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="N67" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O67" s="32" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="P67" s="32" t="n">
-        <v>4.961</v>
-      </c>
-      <c r="Q67" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B68" s="32" t="n">
-        <v>8.778</v>
-      </c>
-      <c r="C68" s="32" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="D68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H68" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr"/>
-      <c r="J68" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O68" s="32" t="n">
-        <v>7.667</v>
-      </c>
-      <c r="P68" s="32" t="n">
-        <v>7.625</v>
-      </c>
-      <c r="Q68" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B69" s="32" t="n">
-        <v>0.956</v>
+        <v>4.712</v>
       </c>
       <c r="C69" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.367</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H69" s="34" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J69" s="36" t="inlineStr">
+        <is>
+          <t>23rd</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>4.8</v>
       </c>
       <c r="O69" s="32" t="n">
-        <v>1.333</v>
+        <v>4.867</v>
       </c>
       <c r="P69" s="32" t="n">
-        <v>1.292</v>
+        <v>4.961</v>
       </c>
       <c r="Q69" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>7.244</v>
+        <v>8.778</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>8.75</v>
+        <v>6.25</v>
       </c>
       <c r="D70" s="32" t="inlineStr">
         <is>
@@ -5185,394 +5035,394 @@
         </is>
       </c>
       <c r="O70" s="32" t="n">
-        <v>9</v>
+        <v>7.667</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>8.417</v>
+        <v>7.625</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B71" s="32" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>1.292</v>
+      </c>
+      <c r="Q71" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="n">
+        <v>7.244</v>
+      </c>
+      <c r="C72" s="32" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="D72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="P72" s="32" t="n">
+        <v>8.417</v>
+      </c>
+      <c r="Q72" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B71" s="32" t="n">
+      <c r="B73" s="32" t="n">
         <v>0.549</v>
       </c>
-      <c r="C71" s="32" t="n">
+      <c r="C73" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="D71" s="32" t="n">
+      <c r="D73" s="32" t="n">
         <v>0.65</v>
       </c>
-      <c r="E71" s="32" t="n">
+      <c r="E73" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="F71" s="32" t="n">
+      <c r="F73" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="G71" s="32" t="n">
+      <c r="G73" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="H71" s="34" t="inlineStr">
+      <c r="H73" s="34" t="inlineStr">
         <is>
           <t>6th</t>
         </is>
       </c>
-      <c r="I71" s="32" t="inlineStr">
+      <c r="I73" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J71" s="36" t="inlineStr">
+      <c r="J73" s="36" t="inlineStr">
         <is>
           <t>27th</t>
         </is>
       </c>
-      <c r="K71" s="32" t="n">
+      <c r="K73" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="L71" s="32" t="n">
+      <c r="L73" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="M71" s="32" t="n">
+      <c r="M73" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="N71" s="32" t="n">
+      <c r="N73" s="32" t="n">
         <v>0.75</v>
       </c>
-      <c r="O71" s="32" t="n">
+      <c r="O73" s="32" t="n">
         <v>0.633</v>
       </c>
-      <c r="P71" s="32" t="n">
+      <c r="P73" s="32" t="n">
         <v>0.653</v>
       </c>
-      <c r="Q71" s="35" t="inlineStr">
+      <c r="Q73" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="29" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="29" t="inlineStr">
         <is>
           <t>Houston Astros offense vs Tampa Bay Rays defense</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="30" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B74" s="30" t="inlineStr">
+      <c r="B76" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C74" s="30" t="inlineStr">
+      <c r="C76" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D74" s="30" t="inlineStr">
+      <c r="D76" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E74" s="30" t="inlineStr">
+      <c r="E76" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F74" s="30" t="inlineStr">
+      <c r="F76" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G74" s="30" t="inlineStr">
+      <c r="G76" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H74" s="30" t="inlineStr">
+      <c r="H76" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I74" s="30" t="inlineStr">
+      <c r="I76" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J74" s="30" t="inlineStr">
+      <c r="J76" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K74" s="30" t="inlineStr">
+      <c r="K76" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L74" s="30" t="inlineStr">
+      <c r="L76" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M74" s="30" t="inlineStr">
+      <c r="M76" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N74" s="30" t="inlineStr">
+      <c r="N76" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O74" s="30" t="inlineStr">
+      <c r="O76" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P74" s="30" t="inlineStr">
+      <c r="P76" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q74" s="30" t="inlineStr">
+      <c r="Q76" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>4.857</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>4.267</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H75" s="34" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="34" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>2.933</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>4.033</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>4.397</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B76" s="32" t="n">
-        <v>8.083</v>
-      </c>
-      <c r="C76" s="32" t="n">
-        <v>7.667</v>
-      </c>
-      <c r="D76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H76" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O76" s="32" t="n">
-        <v>11</v>
-      </c>
-      <c r="P76" s="32" t="n">
-        <v>8.467000000000001</v>
-      </c>
-      <c r="Q76" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B77" s="32" t="n">
-        <v>1.417</v>
+        <v>4.857</v>
       </c>
       <c r="C77" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.6</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H77" s="34" t="inlineStr">
+        <is>
+          <t>10th</t>
         </is>
       </c>
       <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J77" s="34" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>2.933</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>3.4</v>
       </c>
       <c r="O77" s="32" t="n">
-        <v>3.25</v>
+        <v>4.033</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>1.444</v>
+        <v>4.397</v>
       </c>
       <c r="Q77" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>7.729</v>
+        <v>8.083</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>9.333</v>
+        <v>7.667</v>
       </c>
       <c r="D78" s="32" t="inlineStr">
         <is>
@@ -5626,71 +5476,221 @@
         </is>
       </c>
       <c r="O78" s="32" t="n">
-        <v>6.75</v>
+        <v>11</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>7.778</v>
+        <v>8.467000000000001</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B79" s="32" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr"/>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P79" s="32" t="n">
+        <v>1.444</v>
+      </c>
+      <c r="Q79" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B80" s="32" t="n">
+        <v>7.729</v>
+      </c>
+      <c r="C80" s="32" t="n">
+        <v>9.333</v>
+      </c>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="32" t="inlineStr"/>
+      <c r="J80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O80" s="32" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="P80" s="32" t="n">
+        <v>7.778</v>
+      </c>
+      <c r="Q80" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B79" s="32" t="n">
+      <c r="B81" s="32" t="n">
         <v>0.6929999999999999</v>
       </c>
-      <c r="C79" s="32" t="n">
+      <c r="C81" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="D79" s="32" t="n">
+      <c r="D81" s="32" t="n">
         <v>0.75</v>
       </c>
-      <c r="E79" s="32" t="n">
+      <c r="E81" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="F79" s="32" t="n">
+      <c r="F81" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="G79" s="32" t="n">
+      <c r="G81" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="H79" s="36" t="inlineStr">
+      <c r="H81" s="36" t="inlineStr">
         <is>
           <t>21st</t>
         </is>
       </c>
-      <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="33" t="inlineStr">
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="33" t="inlineStr">
         <is>
           <t>16th</t>
         </is>
       </c>
-      <c r="K79" s="32" t="n">
+      <c r="K81" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="L79" s="32" t="n">
+      <c r="L81" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="M79" s="32" t="n">
+      <c r="M81" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="N79" s="32" t="n">
+      <c r="N81" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="O79" s="32" t="n">
+      <c r="O81" s="32" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="P79" s="32" t="n">
+      <c r="P81" s="32" t="n">
         <v>0.493</v>
       </c>
-      <c r="Q79" s="35" t="inlineStr">
+      <c r="Q81" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -5709,7 +5709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:Q80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5726,875 +5726,875 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="29" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="29" t="inlineStr">
         <is>
           <t>Boston Red Sox offense vs Los Angeles Angels defense</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="30" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B64" s="30" t="inlineStr">
+      <c r="B67" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C64" s="30" t="inlineStr">
+      <c r="C67" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D64" s="30" t="inlineStr">
+      <c r="D67" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E64" s="30" t="inlineStr">
+      <c r="E67" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F64" s="30" t="inlineStr">
+      <c r="F67" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G64" s="30" t="inlineStr">
+      <c r="G67" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H64" s="30" t="inlineStr">
+      <c r="H67" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I64" s="30" t="inlineStr">
+      <c r="I67" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J64" s="30" t="inlineStr">
+      <c r="J67" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K64" s="30" t="inlineStr">
+      <c r="K67" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L64" s="30" t="inlineStr">
+      <c r="L67" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M64" s="30" t="inlineStr">
+      <c r="M67" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N64" s="30" t="inlineStr">
+      <c r="N67" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O64" s="30" t="inlineStr">
+      <c r="O67" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P64" s="30" t="inlineStr">
+      <c r="P67" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q64" s="30" t="inlineStr">
+      <c r="Q67" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B65" s="32" t="n">
-        <v>4.123</v>
-      </c>
-      <c r="C65" s="32" t="n">
-        <v>4.233</v>
-      </c>
-      <c r="D65" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E65" s="32" t="n">
-        <v>3.867</v>
-      </c>
-      <c r="F65" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G65" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H65" s="36" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="I65" s="32" t="inlineStr"/>
-      <c r="J65" s="34" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="K65" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L65" s="32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="M65" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N65" s="32" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="O65" s="32" t="n">
-        <v>4.633</v>
-      </c>
-      <c r="P65" s="32" t="n">
-        <v>5.092</v>
-      </c>
-      <c r="Q65" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B66" s="32" t="n">
-        <v>8.304</v>
-      </c>
-      <c r="C66" s="32" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="D66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H66" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I66" s="32" t="inlineStr"/>
-      <c r="J66" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O66" s="32" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="P66" s="32" t="n">
-        <v>8.244999999999999</v>
-      </c>
-      <c r="Q66" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B67" s="32" t="n">
-        <v>0.739</v>
-      </c>
-      <c r="C67" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H67" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I67" s="32" t="inlineStr"/>
-      <c r="J67" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O67" s="32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P67" s="32" t="n">
-        <v>1.061</v>
-      </c>
-      <c r="Q67" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B68" s="32" t="n">
-        <v>8.239000000000001</v>
+        <v>4.123</v>
       </c>
       <c r="C68" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="D68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H68" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.233</v>
+      </c>
+      <c r="D68" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E68" s="32" t="n">
+        <v>3.867</v>
+      </c>
+      <c r="F68" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G68" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H68" s="36" t="inlineStr">
+        <is>
+          <t>21st</t>
         </is>
       </c>
       <c r="I68" s="32" t="inlineStr"/>
-      <c r="J68" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J68" s="34" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L68" s="32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M68" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N68" s="32" t="n">
+        <v>4.45</v>
       </c>
       <c r="O68" s="32" t="n">
-        <v>9</v>
+        <v>4.633</v>
       </c>
       <c r="P68" s="32" t="n">
-        <v>8.816000000000001</v>
+        <v>5.092</v>
       </c>
       <c r="Q68" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="31" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>8.304</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="D69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr"/>
+      <c r="J69" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>8.244999999999999</v>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>0.739</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>1.061</v>
+      </c>
+      <c r="Q70" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B71" s="32" t="n">
+        <v>8.239000000000001</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>8.816000000000001</v>
+      </c>
+      <c r="Q71" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B69" s="32" t="n">
+      <c r="B72" s="32" t="n">
         <v>0.361</v>
       </c>
-      <c r="C69" s="32" t="n">
+      <c r="C72" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="D69" s="32" t="n">
+      <c r="D72" s="32" t="n">
         <v>0.55</v>
       </c>
-      <c r="E69" s="32" t="n">
+      <c r="E72" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="F69" s="32" t="n">
+      <c r="F72" s="32" t="n">
         <v>0.9</v>
       </c>
-      <c r="G69" s="32" t="n">
+      <c r="G72" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="H69" s="34" t="inlineStr">
+      <c r="H72" s="34" t="inlineStr">
         <is>
           <t>3rd</t>
         </is>
       </c>
-      <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="34" t="inlineStr">
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="34" t="inlineStr">
         <is>
           <t>2nd</t>
         </is>
       </c>
-      <c r="K69" s="32" t="n">
+      <c r="K72" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L69" s="32" t="n">
+      <c r="L72" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="M69" s="32" t="n">
+      <c r="M72" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="N69" s="32" t="n">
+      <c r="N72" s="32" t="n">
         <v>0.55</v>
       </c>
-      <c r="O69" s="32" t="n">
+      <c r="O72" s="32" t="n">
         <v>0.767</v>
       </c>
-      <c r="P69" s="32" t="n">
+      <c r="P72" s="32" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="Q69" s="35" t="inlineStr">
+      <c r="Q72" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="29" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="29" t="inlineStr">
         <is>
           <t>Los Angeles Angels offense vs Boston Red Sox defense</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="30" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B72" s="30" t="inlineStr">
+      <c r="B75" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C72" s="30" t="inlineStr">
+      <c r="C75" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D72" s="30" t="inlineStr">
+      <c r="D75" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E72" s="30" t="inlineStr">
+      <c r="E75" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F72" s="30" t="inlineStr">
+      <c r="F75" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G72" s="30" t="inlineStr">
+      <c r="G75" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H72" s="30" t="inlineStr">
+      <c r="H75" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I72" s="30" t="inlineStr">
+      <c r="I75" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J72" s="30" t="inlineStr">
+      <c r="J75" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K72" s="30" t="inlineStr">
+      <c r="K75" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L72" s="30" t="inlineStr">
+      <c r="L75" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M72" s="30" t="inlineStr">
+      <c r="M75" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N72" s="30" t="inlineStr">
+      <c r="N75" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O72" s="30" t="inlineStr">
+      <c r="O75" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P72" s="30" t="inlineStr">
+      <c r="P75" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q72" s="30" t="inlineStr">
+      <c r="Q75" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B73" s="32" t="n">
-        <v>4.592</v>
-      </c>
-      <c r="C73" s="32" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="D73" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E73" s="32" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="F73" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="G73" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H73" s="36" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="33" t="inlineStr">
-        <is>
-          <t>20th</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L73" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="M73" s="32" t="n">
-        <v>3.733</v>
-      </c>
-      <c r="N73" s="32" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O73" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P73" s="32" t="n">
-        <v>4.233</v>
-      </c>
-      <c r="Q73" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>7.714</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="D74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>8.391</v>
-      </c>
-      <c r="Q74" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>1.184</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H75" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>1.217</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B76" s="32" t="n">
-        <v>9.286</v>
+        <v>4.592</v>
       </c>
       <c r="C76" s="32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H76" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>5.067</v>
+      </c>
+      <c r="D76" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E76" s="32" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="F76" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G76" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H76" s="36" t="inlineStr">
+        <is>
+          <t>28th</t>
         </is>
       </c>
       <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J76" s="33" t="inlineStr">
+        <is>
+          <t>20th</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L76" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M76" s="32" t="n">
+        <v>3.733</v>
+      </c>
+      <c r="N76" s="32" t="n">
+        <v>3.95</v>
       </c>
       <c r="O76" s="32" t="n">
-        <v>11</v>
+        <v>3.9</v>
       </c>
       <c r="P76" s="32" t="n">
-        <v>8.587</v>
+        <v>4.233</v>
       </c>
       <c r="Q76" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>7.714</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="D77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr"/>
+      <c r="J77" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O77" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="P77" s="32" t="n">
+        <v>8.391</v>
+      </c>
+      <c r="Q77" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="n">
+        <v>1.184</v>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>1.217</v>
+      </c>
+      <c r="Q78" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B79" s="32" t="n">
+        <v>9.286</v>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr"/>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="P79" s="32" t="n">
+        <v>8.587</v>
+      </c>
+      <c r="Q79" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B77" s="32" t="n">
+      <c r="B80" s="32" t="n">
         <v>0.587</v>
       </c>
-      <c r="C77" s="32" t="n">
+      <c r="C80" s="32" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="D77" s="32" t="n">
+      <c r="D80" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="E77" s="32" t="n">
+      <c r="E80" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="F77" s="32" t="n">
+      <c r="F80" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="G77" s="32" t="n">
+      <c r="G80" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="H77" s="36" t="inlineStr">
+      <c r="H80" s="36" t="inlineStr">
         <is>
           <t>22nd</t>
         </is>
       </c>
-      <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="33" t="inlineStr">
+      <c r="I80" s="32" t="inlineStr"/>
+      <c r="J80" s="33" t="inlineStr">
         <is>
           <t>20th</t>
         </is>
       </c>
-      <c r="K77" s="32" t="n">
+      <c r="K80" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="L77" s="32" t="n">
+      <c r="L80" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="M77" s="32" t="n">
+      <c r="M80" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="N77" s="32" t="n">
+      <c r="N80" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="O77" s="32" t="n">
+      <c r="O80" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="P77" s="32" t="n">
+      <c r="P80" s="32" t="n">
         <v>0.722</v>
       </c>
-      <c r="Q77" s="35" t="inlineStr">
+      <c r="Q80" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -6613,7 +6613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6630,324 +6630,174 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="29" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>Miami Marlins offense vs Athletics defense</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="30" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B68" s="30" t="inlineStr">
+      <c r="B70" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C68" s="30" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D68" s="30" t="inlineStr">
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E68" s="30" t="inlineStr">
+      <c r="E70" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F68" s="30" t="inlineStr">
+      <c r="F70" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G68" s="30" t="inlineStr">
+      <c r="G70" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H68" s="30" t="inlineStr">
+      <c r="H70" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I68" s="30" t="inlineStr">
+      <c r="I70" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J68" s="30" t="inlineStr">
+      <c r="J70" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K68" s="30" t="inlineStr">
+      <c r="K70" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L68" s="30" t="inlineStr">
+      <c r="L70" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M68" s="30" t="inlineStr">
+      <c r="M70" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N68" s="30" t="inlineStr">
+      <c r="N70" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O68" s="30" t="inlineStr">
+      <c r="O70" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P68" s="30" t="inlineStr">
+      <c r="P70" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q68" s="30" t="inlineStr">
+      <c r="Q70" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>4.519</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>4.733</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>5.333</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H69" s="34" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J69" s="36" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>6.367</v>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>5.127</v>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B70" s="32" t="n">
-        <v>8.286</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>8.311999999999999</v>
-      </c>
-      <c r="Q70" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>0.918</v>
+        <v>4.519</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.733</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J71" s="36" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>6.2</v>
       </c>
       <c r="O71" s="32" t="n">
-        <v>0</v>
+        <v>6.367</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>1.271</v>
+        <v>5.127</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>7.816</v>
+        <v>8.286</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>9</v>
+        <v>6.75</v>
       </c>
       <c r="D72" s="32" t="inlineStr">
         <is>
@@ -7001,394 +6851,394 @@
         </is>
       </c>
       <c r="O72" s="32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>8.146000000000001</v>
+        <v>8.311999999999999</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>1.271</v>
+      </c>
+      <c r="Q73" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="n">
+        <v>7.816</v>
+      </c>
+      <c r="C74" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>8.146000000000001</v>
+      </c>
+      <c r="Q74" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B73" s="32" t="n">
+      <c r="B75" s="32" t="n">
         <v>0.547</v>
       </c>
-      <c r="C73" s="32" t="n">
+      <c r="C75" s="32" t="n">
         <v>0.367</v>
       </c>
-      <c r="D73" s="32" t="n">
+      <c r="D75" s="32" t="n">
         <v>0.45</v>
       </c>
-      <c r="E73" s="32" t="n">
+      <c r="E75" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="F73" s="32" t="n">
+      <c r="F75" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="G73" s="32" t="n">
+      <c r="G75" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="H73" s="33" t="inlineStr">
+      <c r="H75" s="33" t="inlineStr">
         <is>
           <t>12th</t>
         </is>
       </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="34" t="inlineStr">
         <is>
           <t>10th</t>
         </is>
       </c>
-      <c r="K73" s="32" t="n">
+      <c r="K75" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="L73" s="32" t="n">
+      <c r="L75" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="M73" s="32" t="n">
+      <c r="M75" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="N73" s="32" t="n">
+      <c r="N75" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="O73" s="32" t="n">
+      <c r="O75" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="P73" s="32" t="n">
+      <c r="P75" s="32" t="n">
         <v>0.653</v>
       </c>
-      <c r="Q73" s="35" t="inlineStr">
+      <c r="Q75" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="29" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>Athletics offense vs Miami Marlins defense</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="30" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B76" s="30" t="inlineStr">
+      <c r="B78" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C76" s="30" t="inlineStr">
+      <c r="C78" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D76" s="30" t="inlineStr">
+      <c r="D78" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E76" s="30" t="inlineStr">
+      <c r="E78" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F76" s="30" t="inlineStr">
+      <c r="F78" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G76" s="30" t="inlineStr">
+      <c r="G78" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H76" s="30" t="inlineStr">
+      <c r="H78" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I76" s="30" t="inlineStr">
+      <c r="I78" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J76" s="30" t="inlineStr">
+      <c r="J78" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K76" s="30" t="inlineStr">
+      <c r="K78" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L76" s="30" t="inlineStr">
+      <c r="L78" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M76" s="30" t="inlineStr">
+      <c r="M78" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N76" s="30" t="inlineStr">
+      <c r="N78" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O76" s="30" t="inlineStr">
+      <c r="O78" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P76" s="30" t="inlineStr">
+      <c r="P78" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q76" s="30" t="inlineStr">
+      <c r="Q78" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>4.709</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>5.433</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>4.667</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H77" s="36" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J77" s="36" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>4.133</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>3.867</v>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>4.312</v>
-      </c>
-      <c r="Q77" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B78" s="32" t="n">
-        <v>8.146000000000001</v>
-      </c>
-      <c r="C78" s="32" t="n">
-        <v>8.667</v>
-      </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O78" s="32" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="P78" s="32" t="n">
-        <v>7.694</v>
-      </c>
-      <c r="Q78" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>1.062</v>
+        <v>4.709</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="D79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.433</v>
+      </c>
+      <c r="D79" s="32" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="E79" s="32" t="n">
+        <v>4.667</v>
+      </c>
+      <c r="F79" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G79" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H79" s="36" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J79" s="36" t="inlineStr">
+        <is>
+          <t>28th</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L79" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M79" s="32" t="n">
+        <v>4.133</v>
+      </c>
+      <c r="N79" s="32" t="n">
+        <v>3.85</v>
       </c>
       <c r="O79" s="32" t="n">
-        <v>1.5</v>
+        <v>3.867</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>1.082</v>
+        <v>4.312</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>8.625</v>
+        <v>8.146000000000001</v>
       </c>
       <c r="C80" s="32" t="n">
-        <v>8.333</v>
+        <v>8.667</v>
       </c>
       <c r="D80" s="32" t="inlineStr">
         <is>
@@ -7442,71 +7292,221 @@
         </is>
       </c>
       <c r="O80" s="32" t="n">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>8.531000000000001</v>
+        <v>7.694</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P81" s="32" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="Q81" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="n">
+        <v>8.625</v>
+      </c>
+      <c r="C82" s="32" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="D82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="P82" s="32" t="n">
+        <v>8.531000000000001</v>
+      </c>
+      <c r="Q82" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B81" s="32" t="n">
+      <c r="B83" s="32" t="n">
         <v>0.64</v>
       </c>
-      <c r="C81" s="32" t="n">
+      <c r="C83" s="32" t="n">
         <v>0.9330000000000001</v>
       </c>
-      <c r="D81" s="32" t="n">
+      <c r="D83" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="E81" s="32" t="n">
+      <c r="E83" s="32" t="n">
         <v>0.9330000000000001</v>
       </c>
-      <c r="F81" s="32" t="n">
+      <c r="F83" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="G81" s="32" t="n">
+      <c r="G83" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="H81" s="36" t="inlineStr">
+      <c r="H83" s="36" t="inlineStr">
         <is>
           <t>23rd</t>
         </is>
       </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="33" t="inlineStr">
+      <c r="I83" s="32" t="inlineStr"/>
+      <c r="J83" s="33" t="inlineStr">
         <is>
           <t>17th</t>
         </is>
       </c>
-      <c r="K81" s="32" t="n">
+      <c r="K83" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="L81" s="32" t="n">
+      <c r="L83" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="M81" s="32" t="n">
+      <c r="M83" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="N81" s="32" t="n">
+      <c r="N83" s="32" t="n">
         <v>0.45</v>
       </c>
-      <c r="O81" s="32" t="n">
+      <c r="O83" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="P81" s="32" t="n">
+      <c r="P83" s="32" t="n">
         <v>0.64</v>
       </c>
-      <c r="Q81" s="35" t="inlineStr">
+      <c r="Q83" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7723,17 +7723,17 @@
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -7743,17 +7743,17 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>New York Mets +1.5</t>
+          <t>Baltimore Orioles +1.5</t>
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6918631178707224</v>
+        <v>0.6947407407407407</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-225</v>
+        <v>-228</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 69.2% (fair -225). Your call.</t>
+          <t>Model 69.5% (fair -228). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -7794,12 +7794,12 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -7809,17 +7809,17 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox +1.5</t>
+          <t>New York Mets +1.5</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6199629629629629</v>
+        <v>0.6918631178707224</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-163</v>
+        <v>-225</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -7843,7 +7843,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 62.0% (fair -163). Your call.</t>
+          <t>Model 69.2% (fair -225). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -7860,12 +7860,12 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Los Angeles Angels</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>01:38</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -7875,14 +7875,14 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox +1.5</t>
+          <t>Chicago White Sox +1.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.596</v>
+        <v>0.6191481481481481</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-148</v>
+        <v>-163</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>170</v>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 59.6% (fair -148). Your call.</t>
+          <t>Model 61.9% (fair -163). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -7926,12 +7926,12 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>01:38</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates +1.5</t>
+          <t>Boston Red Sox +1.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6662946859903381</v>
+        <v>0.596</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-200</v>
+        <v>-148</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-107</v>
+        <v>170</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -7975,7 +7975,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 66.6% (fair -200). Your call.</t>
+          <t>Model 59.6% (fair -148). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -7987,37 +7987,37 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Los Angeles Angels</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>01:38</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Pittsburgh Pirates +1.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.535304347826087</v>
+        <v>0.6663046511627908</v>
       </c>
       <c r="G9" s="14" t="n">
+        <v>-200</v>
+      </c>
+      <c r="H9" s="15" t="n">
         <v>-115</v>
-      </c>
-      <c r="H9" s="15" t="n">
-        <v>130</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 66.6% (fair -200). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8053,7 +8053,7 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
@@ -8068,22 +8068,22 @@
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels -1.5</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.404</v>
+        <v>0.5352863436123348</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>148</v>
+        <v>-115</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>185</v>
+        <v>127</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8107,7 +8107,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 40.4% (fair +148). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8124,32 +8124,32 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>01:38</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Los Angeles Angels -1.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.3767326732673267</v>
+        <v>0.404</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 37.7% (fair +165). Your call.</t>
+          <t>Model 40.4% (fair +148). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8185,37 +8185,37 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5321126760563381</v>
+        <v>0.3767326732673267</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-114</v>
+        <v>165</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>113</v>
+        <v>203</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 37.7% (fair +165). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4693697478991597</v>
+        <v>0.4737768240343348</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 46.9% (fair +113). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8454,12 +8454,12 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Athletics</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -8469,17 +8469,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins +1.5</t>
+          <t>Chicago Cubs -1.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5757694835680751</v>
+        <v>0.42375</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-136</v>
+        <v>136</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-113</v>
+        <v>156</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8503,7 +8503,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8520,32 +8520,32 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>Miami Marlins @ Athletics</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Athletics -1.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5755042253521127</v>
+        <v>0.4316</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-136</v>
+        <v>132</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-113</v>
+        <v>150</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 43.2% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8586,12 +8586,12 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Miami Marlins @ Athletics</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -8601,17 +8601,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs -1.5</t>
+          <t>Miami Marlins +1.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.42375</v>
+        <v>0.5684</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>136</v>
+        <v>-132</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>156</v>
+        <v>-112</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 56.8% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -8647,37 +8647,37 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Athletics</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5264563106796116</v>
+        <v>0.4083269961977187</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-111</v>
+        <v>145</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>106</v>
+        <v>163</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 40.8% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -8713,17 +8713,17 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4083269961977187</v>
+        <v>0.5780986175115207</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>145</v>
+        <v>-137</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>163</v>
+        <v>-117</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 40.8% (fair +145). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -8784,12 +8784,12 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Athletics</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -8799,17 +8799,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Athletics -1.5</t>
+          <t>Minnesota Twins +1.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4242687747035572</v>
+        <v>0.525911330049261</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>136</v>
+        <v>-111</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>153</v>
+        <v>103</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -8850,32 +8850,32 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Miami Marlins @ Athletics</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins +1.5</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5315</v>
+        <v>0.5079523809523809</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-113</v>
+        <v>-103</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -8899,7 +8899,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -8926,22 +8926,22 @@
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Over 10</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.6202622950819672</v>
+        <v>0.53095</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-163</v>
+        <v>-113</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-144</v>
+        <v>100</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -8965,7 +8965,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 62.0% (fair -163). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -8977,17 +8977,17 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -8997,17 +8997,17 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5178217821782178</v>
+        <v>0.6188788381742738</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-107</v>
+        <v>-162</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>102</v>
+        <v>-141</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -9031,7 +9031,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -107). Your call.</t>
+          <t>Model 61.9% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9048,32 +9048,32 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals +1.5</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5762548672566372</v>
+        <v>0.52095</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-136</v>
+        <v>-109</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-126</v>
+        <v>100</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -9109,7 +9109,7 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
@@ -9119,27 +9119,27 @@
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>St. Louis Cardinals +1.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4331932773109243</v>
+        <v>0.5762548672566372</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>131</v>
+        <v>-136</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>138</v>
+        <v>-126</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -9163,7 +9163,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 43.3% (fair +131). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -9180,32 +9180,32 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates -1.5</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5151</v>
+        <v>0.4331932773109243</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-106</v>
+        <v>131</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -9229,7 +9229,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -9246,32 +9246,32 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.4477826086956522</v>
+        <v>0.5151</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>123</v>
+        <v>-106</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -9295,7 +9295,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 44.8% (fair +123). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -9307,37 +9307,37 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.526229268292683</v>
+        <v>0.4628378378378379</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-111</v>
+        <v>116</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-105</v>
+        <v>122</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -9361,7 +9361,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -9934,13 +9934,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4693697478991597</v>
+        <v>0.4737768240343348</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 46.9% (fair +113). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -10000,13 +10000,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.530617094017094</v>
+        <v>0.5262362068965517</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-113</v>
+        <v>-111</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-134</v>
+        <v>-132</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -10062,7 +10062,7 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 10.5</t>
+          <t>Over 10</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
@@ -10072,7 +10072,7 @@
         <v>-101</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -10128,7 +10128,7 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Under 10</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
@@ -10198,13 +10198,13 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.333688524590164</v>
+        <v>0.33372</v>
       </c>
       <c r="G15" s="14" t="n">
         <v>200</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -10264,13 +10264,13 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.6662946859903381</v>
+        <v>0.6663046511627908</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>-200</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-107</v>
+        <v>-115</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -10594,13 +10594,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4685</v>
+        <v>0.4740666666666666</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -10624,7 +10624,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 46.9% (fair +113). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -10660,13 +10660,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5315</v>
+        <v>0.525911330049261</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-113</v>
+        <v>-111</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -10690,7 +10690,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10726,13 +10726,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5755042253521127</v>
+        <v>0.5780986175115207</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-136</v>
+        <v>-137</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-113</v>
+        <v>-117</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10756,7 +10756,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10792,10 +10792,10 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4245116279069767</v>
+        <v>0.4219069767441861</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H24" s="15" t="n">
         <v>115</v>
@@ -10822,7 +10822,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 42.5% (fair +136). Your call.</t>
+          <t>Model 42.2% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10930,7 +10930,7 @@
         <v>110</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10990,13 +10990,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4633181818181819</v>
+        <v>0.4628378378378379</v>
       </c>
       <c r="G27" s="14" t="n">
         <v>116</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -11056,13 +11056,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5366900900900901</v>
+        <v>0.5371636363636363</v>
       </c>
       <c r="G28" s="14" t="n">
         <v>-116</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-122</v>
+        <v>-120</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -11122,10 +11122,10 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5347</v>
+        <v>0.4883</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-115</v>
+        <v>105</v>
       </c>
       <c r="H29" s="15" t="n">
         <v>117</v>
@@ -11152,7 +11152,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -11188,13 +11188,13 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.4653</v>
+        <v>0.5117</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>115</v>
+        <v>-105</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -11254,7 +11254,7 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.3800374531835206</v>
+        <v>0.3808614232209738</v>
       </c>
       <c r="G31" s="14" t="n">
         <v>163</v>
@@ -11284,7 +11284,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 38.0% (fair +163). Your call.</t>
+          <t>Model 38.1% (fair +163). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -11320,7 +11320,7 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.6199629629629629</v>
+        <v>0.6191481481481481</v>
       </c>
       <c r="G32" s="14" t="n">
         <v>-163</v>
@@ -11350,7 +11350,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 62.0% (fair -163). Your call.</t>
+          <t>Model 61.9% (fair -163). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -11386,13 +11386,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.5178217821782178</v>
+        <v>0.52095</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>-107</v>
+        <v>-109</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -11416,7 +11416,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -107). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -11452,13 +11452,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.4821725490196078</v>
+        <v>0.4790465346534653</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-104</v>
+        <v>-102</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -11482,7 +11482,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +107). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -11590,7 +11590,7 @@
         <v>-158</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -11782,7 +11782,7 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.5710764705882353</v>
+        <v>0.570844537815126</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>-133</v>
@@ -11848,7 +11848,7 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.4289495798319328</v>
+        <v>0.4291596638655463</v>
       </c>
       <c r="G40" s="14" t="n">
         <v>133</v>
@@ -11914,13 +11914,13 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.4907804878048781</v>
+        <v>0.4517</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -11980,13 +11980,13 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5092116504854369</v>
+        <v>0.5483</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-104</v>
+        <v>-121</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-106</v>
+        <v>114</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -12010,7 +12010,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -12046,13 +12046,13 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.5133215686274509</v>
+        <v>0.5102</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>-105</v>
+        <v>-104</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -12076,7 +12076,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -12112,10 +12112,10 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.4866336633663366</v>
+        <v>0.4898019801980198</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H44" s="15" t="n">
         <v>102</v>
@@ -12142,7 +12142,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -12184,7 +12184,7 @@
         <v>114</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>-101</v>
+        <v>100</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -12316,7 +12316,7 @@
         <v>119</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -12382,7 +12382,7 @@
         <v>-119</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-104</v>
+        <v>-106</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -12514,7 +12514,7 @@
         <v>-103</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -12706,13 +12706,13 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4402173913043478</v>
+        <v>0.4400881057268722</v>
       </c>
       <c r="G53" s="14" t="n">
         <v>127</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -12772,7 +12772,7 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5597511013215859</v>
+        <v>0.5599189427312775</v>
       </c>
       <c r="G54" s="14" t="n">
         <v>-127</v>
@@ -12838,10 +12838,10 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.4735384615384615</v>
+        <v>0.4920230769230769</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="H55" s="15" t="n">
         <v>-108</v>
@@ -12868,7 +12868,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -12904,13 +12904,13 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.5264563106796116</v>
+        <v>0.5079523809523809</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-111</v>
+        <v>-103</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -12934,7 +12934,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -12970,13 +12970,13 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.4242687747035572</v>
+        <v>0.4316</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -13000,7 +13000,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 43.2% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -13036,13 +13036,13 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5757694835680751</v>
+        <v>0.5684</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-136</v>
+        <v>-132</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>-113</v>
+        <v>-112</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 56.8% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -13102,10 +13102,10 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>-196</v>
+        <v>-201</v>
       </c>
       <c r="H59" s="15" t="n"/>
       <c r="I59" s="13">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 66.2% (fair -196). Your call.</t>
+          <t>Model 66.8% (fair -201). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -13166,10 +13166,10 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.3382</v>
+        <v>0.3322</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H60" s="15" t="n"/>
       <c r="I60" s="13">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 33.8% (fair +196). Your call.</t>
+          <t>Model 33.2% (fair +201). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -13230,10 +13230,10 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.3931</v>
+        <v>0.3892</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H61" s="15" t="n"/>
       <c r="I61" s="13">
@@ -13258,7 +13258,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 39.3% (fair +154). Your call.</t>
+          <t>Model 38.9% (fair +157). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -13294,10 +13294,10 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.6069</v>
+        <v>0.6108</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-154</v>
+        <v>-157</v>
       </c>
       <c r="H62" s="15" t="n"/>
       <c r="I62" s="13">
@@ -13322,7 +13322,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 60.7% (fair -154). Your call.</t>
+          <t>Model 61.1% (fair -157). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -13358,7 +13358,7 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.5416</v>
+        <v>0.5405</v>
       </c>
       <c r="G63" s="14" t="n">
         <v>-118</v>
@@ -13386,7 +13386,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -118). Your call.</t>
+          <t>Model 54.0% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -13422,7 +13422,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.4583</v>
+        <v>0.4595</v>
       </c>
       <c r="G64" s="14" t="n">
         <v>118</v>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 45.8% (fair +118). Your call.</t>
+          <t>Model 46.0% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -13486,13 +13486,13 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.6202622950819672</v>
+        <v>0.6188788381742738</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>-163</v>
+        <v>-162</v>
       </c>
       <c r="H65" s="15" t="n">
-        <v>-144</v>
+        <v>-141</v>
       </c>
       <c r="I65" s="13">
         <f>IF($H$65="","",IF($H$65&lt;0,-$H$65/(-$H$65+100),100/($H$65+100)))</f>
@@ -13516,7 +13516,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 62.0% (fair -163). Your call.</t>
+          <t>Model 61.9% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -13552,10 +13552,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.3797478991596639</v>
+        <v>0.3811344537815126</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H66" s="15" t="n">
         <v>138</v>
@@ -13582,7 +13582,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 38.0% (fair +163). Your call.</t>
+          <t>Model 38.1% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -13614,17 +13614,17 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Over 10.5</t>
+          <t>Over 10</t>
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.5792</v>
+        <v>0.53095</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>-138</v>
+        <v>-113</v>
       </c>
       <c r="H67" s="15" t="n">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="I67" s="13">
         <f>IF($H$67="","",IF($H$67&lt;0,-$H$67/(-$H$67+100),100/($H$67+100)))</f>
@@ -13648,7 +13648,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 57.9% (fair -138). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -13680,14 +13680,14 @@
       </c>
       <c r="E68" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Under 10</t>
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.4208</v>
+        <v>0.4690686274509804</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="H68" s="15" t="n">
         <v>104</v>
@@ -13714,7 +13714,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 42.1% (fair +138). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -14278,10 +14278,10 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.50525</v>
+        <v>0.50685</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>-102</v>
+        <v>-103</v>
       </c>
       <c r="H77" s="15" t="n">
         <v>100</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 50.5% (fair -102). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.49475</v>
+        <v>0.4931188118811881</v>
       </c>
       <c r="G78" s="14" t="n">
+        <v>103</v>
+      </c>
+      <c r="H78" s="15" t="n">
         <v>102</v>
-      </c>
-      <c r="H78" s="15" t="n">
-        <v>100</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -14374,7 +14374,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 49.5% (fair +102). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -14482,7 +14482,7 @@
         <v>150</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -14542,13 +14542,13 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.6139245283018868</v>
+        <v>0.6132022813688213</v>
       </c>
       <c r="G81" s="14" t="n">
         <v>-159</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>-165</v>
+        <v>-163</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -14572,7 +14572,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 61.4% (fair -159). Your call.</t>
+          <t>Model 61.3% (fair -159). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -14608,7 +14608,7 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.38609375</v>
+        <v>0.386796875</v>
       </c>
       <c r="G82" s="14" t="n">
         <v>159</v>
@@ -14638,7 +14638,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 38.6% (fair +159). Your call.</t>
+          <t>Model 38.7% (fair +159). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -14674,13 +14674,13 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4158921161825726</v>
+        <v>0.4206722689075631</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -14704,7 +14704,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +140). Your call.</t>
+          <t>Model 42.1% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -14740,13 +14740,13 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5840852459016393</v>
+        <v>0.5793100840336134</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-140</v>
+        <v>-138</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>-144</v>
+        <v>-138</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -14770,7 +14770,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -140). Your call.</t>
+          <t>Model 57.9% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -15334,13 +15334,13 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.3400359712230215</v>
+        <v>0.3052651515151516</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>194</v>
+        <v>228</v>
       </c>
       <c r="H93" s="15" t="n">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="I93" s="13">
         <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
@@ -15364,7 +15364,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 34.0% (fair +194). Your call.</t>
+          <t>Model 30.5% (fair +228). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -15400,13 +15400,13 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.6599571428571428</v>
+        <v>0.6947407407407407</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>-194</v>
+        <v>-228</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>-180</v>
+        <v>170</v>
       </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
@@ -15430,7 +15430,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 66.0% (fair -194). Your call.</t>
+          <t>Model 69.5% (fair -228). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -15598,10 +15598,10 @@
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.5321126760563381</v>
+        <v>0.6342</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>-114</v>
+        <v>-173</v>
       </c>
       <c r="H97" s="15" t="n">
         <v>113</v>
@@ -15628,7 +15628,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 63.4% (fair -173). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -15664,13 +15664,13 @@
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.4678922330097087</v>
+        <v>0.3658</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>114</v>
+        <v>173</v>
       </c>
       <c r="H98" s="15" t="n">
-        <v>-106</v>
+        <v>102</v>
       </c>
       <c r="I98" s="13">
         <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
@@ -15694,7 +15694,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 36.6% (fair +173). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -15730,13 +15730,13 @@
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.6317079136690648</v>
+        <v>0.6279925925925925</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>-172</v>
+        <v>-169</v>
       </c>
       <c r="H99" s="15" t="n">
-        <v>-178</v>
+        <v>-170</v>
       </c>
       <c r="I99" s="13">
         <f>IF($H$99="","",IF($H$99&lt;0,-$H$99/(-$H$99+100),100/($H$99+100)))</f>
@@ -15760,7 +15760,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 63.2% (fair -172). Your call.</t>
+          <t>Model 62.8% (fair -169). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -15796,13 +15796,13 @@
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.3683018867924528</v>
+        <v>0.3719771863117871</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H100" s="15" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
@@ -15826,7 +15826,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 36.8% (fair +172). Your call.</t>
+          <t>Model 37.2% (fair +169). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -15862,13 +15862,13 @@
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.4477826086956522</v>
+        <v>0.4498678414096917</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H101" s="15" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I101" s="13">
         <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
@@ -15892,7 +15892,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 44.8% (fair +123). Your call.</t>
+          <t>Model 45.0% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -15928,10 +15928,10 @@
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.5522068669527898</v>
+        <v>0.5501519313304721</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>-123</v>
+        <v>-122</v>
       </c>
       <c r="H102" s="15" t="n">
         <v>-133</v>
@@ -15958,7 +15958,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 55.0% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -16126,10 +16126,10 @@
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.380532319391635</v>
+        <v>0.3788212927756654</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H105" s="15" t="n">
         <v>163</v>
@@ -16156,7 +16156,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 38.1% (fair +163). Your call.</t>
+          <t>Model 37.9% (fair +164). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -16192,13 +16192,13 @@
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.6194660377358491</v>
+        <v>0.6211925925925925</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>-163</v>
+        <v>-164</v>
       </c>
       <c r="H106" s="15" t="n">
-        <v>-165</v>
+        <v>-170</v>
       </c>
       <c r="I106" s="13">
         <f>IF($H$106="","",IF($H$106&lt;0,-$H$106/(-$H$106+100),100/($H$106+100)))</f>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 61.9% (fair -163). Your call.</t>
+          <t>Model 62.1% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -16858,7 +16858,7 @@
         <v>-152</v>
       </c>
       <c r="H116" s="15" t="n">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="I116" s="13">
         <f>IF($H$116="","",IF($H$116&lt;0,-$H$116/(-$H$116+100),100/($H$116+100)))</f>
@@ -17050,10 +17050,10 @@
         </is>
       </c>
       <c r="F119" s="13" t="n">
-        <v>0.5528</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="G119" s="14" t="n">
-        <v>-124</v>
+        <v>-120</v>
       </c>
       <c r="H119" s="15" t="n"/>
       <c r="I119" s="13">
@@ -17078,7 +17078,7 @@
       </c>
       <c r="N119" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 54.5% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O119" s="15" t="n"/>
@@ -17114,10 +17114,10 @@
         </is>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.4472</v>
+        <v>0.4551</v>
       </c>
       <c r="G120" s="14" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H120" s="15" t="n"/>
       <c r="I120" s="13">
@@ -17142,7 +17142,7 @@
       </c>
       <c r="N120" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 45.5% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O120" s="15" t="n"/>
@@ -17178,13 +17178,13 @@
         </is>
       </c>
       <c r="F121" s="13" t="n">
-        <v>0.5864420168067227</v>
+        <v>0.5839442060085837</v>
       </c>
       <c r="G121" s="14" t="n">
-        <v>-142</v>
+        <v>-140</v>
       </c>
       <c r="H121" s="15" t="n">
-        <v>-138</v>
+        <v>-133</v>
       </c>
       <c r="I121" s="13">
         <f>IF($H$121="","",IF($H$121&lt;0,-$H$121/(-$H$121+100),100/($H$121+100)))</f>
@@ -17208,7 +17208,7 @@
       </c>
       <c r="N121" s="19" t="inlineStr">
         <is>
-          <t>Model 58.6% (fair -142). Your call.</t>
+          <t>Model 58.4% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O121" s="15" t="n"/>
@@ -17244,10 +17244,10 @@
         </is>
       </c>
       <c r="F122" s="13" t="n">
-        <v>0.413519313304721</v>
+        <v>0.4160085836909871</v>
       </c>
       <c r="G122" s="14" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H122" s="15" t="n">
         <v>133</v>
@@ -17274,7 +17274,7 @@
       </c>
       <c r="N122" s="19" t="inlineStr">
         <is>
-          <t>Model 41.4% (fair +142). Your call.</t>
+          <t>Model 41.6% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O122" s="15" t="n"/>
@@ -17442,13 +17442,13 @@
         </is>
       </c>
       <c r="F125" s="13" t="n">
-        <v>0.5353162162162162</v>
+        <v>0.5411766519823789</v>
       </c>
       <c r="G125" s="14" t="n">
-        <v>-115</v>
+        <v>-118</v>
       </c>
       <c r="H125" s="15" t="n">
-        <v>-122</v>
+        <v>-127</v>
       </c>
       <c r="I125" s="13">
         <f>IF($H$125="","",IF($H$125&lt;0,-$H$125/(-$H$125+100),100/($H$125+100)))</f>
@@ -17472,7 +17472,7 @@
       </c>
       <c r="N125" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O125" s="15" t="n"/>
@@ -17508,13 +17508,13 @@
         </is>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.4646948356807512</v>
+        <v>0.4588018433179724</v>
       </c>
       <c r="G126" s="14" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H126" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I126" s="13">
         <f>IF($H$126="","",IF($H$126&lt;0,-$H$126/(-$H$126+100),100/($H$126+100)))</f>
@@ -17538,7 +17538,7 @@
       </c>
       <c r="N126" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O126" s="15" t="n"/>
@@ -17574,13 +17574,13 @@
         </is>
       </c>
       <c r="F127" s="13" t="n">
-        <v>0.535304347826087</v>
+        <v>0.5352863436123348</v>
       </c>
       <c r="G127" s="14" t="n">
         <v>-115</v>
       </c>
       <c r="H127" s="15" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I127" s="13">
         <f>IF($H$127="","",IF($H$127&lt;0,-$H$127/(-$H$127+100),100/($H$127+100)))</f>

--- a/data/output/workbook/2026-07-03.xlsx
+++ b/data/output/workbook/2026-07-03.xlsx
@@ -340,7 +340,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="11001375"/>
+    <ext cx="10125075" cy="10734675"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -370,7 +370,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10801350"/>
+    <ext cx="10125075" cy="10544175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -400,7 +400,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10763250"/>
+    <ext cx="10125075" cy="10506075"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -430,7 +430,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10953750"/>
+    <ext cx="10125075" cy="10696575"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -953,7 +953,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03 18:15</t>
+          <t>2026-07-03 20:14</t>
         </is>
       </c>
     </row>
@@ -6613,7 +6613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6630,174 +6630,324 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Miami Marlins offense vs Athletics defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>Miami Marlins offense vs Athletics defense</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>4.519</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>4.733</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H69" s="34" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J69" s="36" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>6.367</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>5.127</v>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>8.286</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>8.311999999999999</v>
+      </c>
+      <c r="Q70" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>4.519</v>
+        <v>0.918</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>4.733</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>5.333</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J71" s="36" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>6.2</v>
+        <v>1.75</v>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O71" s="32" t="n">
-        <v>6.367</v>
+        <v>0</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>5.127</v>
+        <v>1.271</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>8.286</v>
+        <v>7.816</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>6.75</v>
+        <v>9</v>
       </c>
       <c r="D72" s="32" t="inlineStr">
         <is>
@@ -6851,394 +7001,394 @@
         </is>
       </c>
       <c r="O72" s="32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>8.311999999999999</v>
+        <v>8.146000000000001</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>0.918</v>
+        <v>0.547</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.367</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H73" s="33" t="inlineStr">
+        <is>
+          <t>12th</t>
         </is>
       </c>
       <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="34" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>0.4</v>
       </c>
       <c r="O73" s="32" t="n">
-        <v>0</v>
+        <v>0.533</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>1.271</v>
+        <v>0.653</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>7.816</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="D74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="P74" s="32" t="n">
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>Athletics offense vs Miami Marlins defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>4.709</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>5.433</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>4.667</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H77" s="36" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J77" s="36" t="inlineStr">
+        <is>
+          <t>28th</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>4.133</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O77" s="32" t="n">
+        <v>3.867</v>
+      </c>
+      <c r="P77" s="32" t="n">
+        <v>4.312</v>
+      </c>
+      <c r="Q77" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="n">
         <v>8.146000000000001</v>
       </c>
-      <c r="Q74" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>0.547</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H75" s="33" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="34" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>0.653</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>Athletics offense vs Miami Marlins defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="C78" s="32" t="n">
+        <v>8.667</v>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="32" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>7.694</v>
+      </c>
+      <c r="Q78" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>4.709</v>
+        <v>1.062</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>5.433</v>
-      </c>
-      <c r="D79" s="32" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="E79" s="32" t="n">
-        <v>4.667</v>
-      </c>
-      <c r="F79" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G79" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H79" s="36" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="I79" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J79" s="36" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L79" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="M79" s="32" t="n">
-        <v>4.133</v>
-      </c>
-      <c r="N79" s="32" t="n">
-        <v>3.85</v>
+        <v>2</v>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr"/>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O79" s="32" t="n">
-        <v>3.867</v>
+        <v>1.5</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>4.312</v>
+        <v>1.082</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>8.146000000000001</v>
+        <v>8.625</v>
       </c>
       <c r="C80" s="32" t="n">
-        <v>8.667</v>
+        <v>8.333</v>
       </c>
       <c r="D80" s="32" t="inlineStr">
         <is>
@@ -7292,221 +7442,71 @@
         </is>
       </c>
       <c r="O80" s="32" t="n">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>7.694</v>
+        <v>8.531000000000001</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>1.062</v>
+        <v>0.64</v>
       </c>
       <c r="C81" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="D81" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="32" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="F81" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G81" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H81" s="36" t="inlineStr">
+        <is>
+          <t>23rd</t>
         </is>
       </c>
       <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J81" s="33" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L81" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M81" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="N81" s="32" t="n">
+        <v>0.45</v>
       </c>
       <c r="O81" s="32" t="n">
-        <v>1.5</v>
+        <v>0.467</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>1.082</v>
+        <v>0.64</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="n">
-        <v>8.625</v>
-      </c>
-      <c r="C82" s="32" t="n">
-        <v>8.333</v>
-      </c>
-      <c r="D82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O82" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>8.531000000000001</v>
-      </c>
-      <c r="Q82" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="32" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="C83" s="32" t="n">
-        <v>0.9330000000000001</v>
-      </c>
-      <c r="D83" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E83" s="32" t="n">
-        <v>0.9330000000000001</v>
-      </c>
-      <c r="F83" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G83" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H83" s="36" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="I83" s="32" t="inlineStr"/>
-      <c r="J83" s="33" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="K83" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L83" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M83" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="N83" s="32" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="O83" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="P83" s="32" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="Q83" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7747,10 +7747,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6947407407407407</v>
+        <v>0.703037037037037</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-228</v>
+        <v>-237</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>170</v>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 69.5% (fair -228). Your call.</t>
+          <t>Model 70.3% (fair -237). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -7813,10 +7813,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6918631178707224</v>
+        <v>0.6952851711026616</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-225</v>
+        <v>-228</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>163</v>
@@ -7843,7 +7843,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 69.2% (fair -225). Your call.</t>
+          <t>Model 69.5% (fair -228). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -7879,13 +7879,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6191481481481481</v>
+        <v>0.6191636363636364</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>-163</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -7945,13 +7945,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.596</v>
+        <v>0.5989090909090909</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-148</v>
+        <v>-149</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -7975,7 +7975,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 59.6% (fair -148). Your call.</t>
+          <t>Model 59.9% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -8011,10 +8011,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.6663046511627908</v>
+        <v>0.6753976744186047</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-200</v>
+        <v>-208</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>-115</v>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 66.6% (fair -200). Your call.</t>
+          <t>Model 67.5% (fair -208). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8124,32 +8124,32 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Los Angeles Angels</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>01:38</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels -1.5</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.404</v>
+        <v>0.3771475409836066</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 40.4% (fair +148). Your call.</t>
+          <t>Model 37.7% (fair +165). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8190,32 +8190,32 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>01:38</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Los Angeles Angels -1.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.3767326732673267</v>
+        <v>0.4010877192982456</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 37.7% (fair +165). Your call.</t>
+          <t>Model 40.1% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8251,37 +8251,37 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4737768240343348</v>
+        <v>0.555</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>111</v>
+        <v>-125</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.426640625</v>
+        <v>0.426796875</v>
       </c>
       <c r="G14" s="14" t="n">
         <v>134</v>
@@ -8383,37 +8383,37 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>Miami Marlins @ Athletics</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5016589861751153</v>
+        <v>0.5249038461538462</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-101</v>
+        <v>-110</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8437,7 +8437,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 52.5% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8454,32 +8454,32 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs -1.5</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.42375</v>
+        <v>0.4795154185022026</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8503,7 +8503,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 48.0% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8515,37 +8515,37 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Athletics</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Athletics -1.5</t>
+          <t>Under 10</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4316</v>
+        <v>0.5333823529411765</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>132</v>
+        <v>-114</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>150</v>
+        <v>104</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 43.2% (fair +132). Your call.</t>
+          <t>Model 53.3% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8581,37 +8581,37 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Athletics</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins +1.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5684</v>
+        <v>0.5089201877934273</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-132</v>
+        <v>-104</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-112</v>
+        <v>113</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 56.8% (fair -132). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -8652,12 +8652,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -8667,17 +8667,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4083269961977187</v>
+        <v>0.5075586854460093</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>145</v>
+        <v>-103</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 40.8% (fair +145). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -8718,32 +8718,32 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Minnesota Twins +1.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5780986175115207</v>
+        <v>0.5242233009708738</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-137</v>
+        <v>-110</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-117</v>
+        <v>106</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 57.8% (fair -137). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -8784,12 +8784,12 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Miami Marlins @ Athletics</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -8799,17 +8799,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins +1.5</t>
+          <t>Miami Marlins +1.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.525911330049261</v>
+        <v>0.5757488372093024</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-111</v>
+        <v>-136</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>103</v>
+        <v>-115</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -8850,32 +8850,32 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Athletics</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5079523809523809</v>
+        <v>0.5784760368663594</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-103</v>
+        <v>-137</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>110</v>
+        <v>-117</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -8899,7 +8899,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -8911,37 +8911,37 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Over 10</t>
+          <t>St. Louis Cardinals +1.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.53095</v>
+        <v>0.5945973451327434</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-113</v>
+        <v>-147</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>100</v>
+        <v>-126</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -8965,7 +8965,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 59.5% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -8982,12 +8982,12 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -8997,17 +8997,17 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.6188788381742738</v>
+        <v>0.414296875</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-162</v>
+        <v>141</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-141</v>
+        <v>156</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -9031,7 +9031,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 61.9% (fair -162). Your call.</t>
+          <t>Model 41.4% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9048,32 +9048,32 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Miami Marlins @ Athletics</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Athletics -1.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.52095</v>
+        <v>0.42424</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-109</v>
+        <v>136</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -9109,7 +9109,7 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
@@ -9119,27 +9119,27 @@
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals +1.5</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5762548672566372</v>
+        <v>0.4331147540983606</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-136</v>
+        <v>131</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-126</v>
+        <v>144</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -9163,7 +9163,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -9180,12 +9180,12 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -9195,17 +9195,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4331932773109243</v>
+        <v>0.6208524590163935</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>131</v>
+        <v>-164</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>138</v>
+        <v>-144</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -9229,7 +9229,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 43.3% (fair +131). Your call.</t>
+          <t>Model 62.1% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -9241,37 +9241,37 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates -1.5</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5151</v>
+        <v>0.5195544554455446</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-106</v>
+        <v>-108</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -9295,7 +9295,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -9307,37 +9307,37 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.4628378378378379</v>
+        <v>0.5334512195121952</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>116</v>
+        <v>-114</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>122</v>
+        <v>-105</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -9361,7 +9361,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 53.3% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -9538,10 +9538,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4500900900900902</v>
+        <v>0.457927927927928</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>122</v>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 45.0% (fair +122). Your call.</t>
+          <t>Model 45.8% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -9604,10 +9604,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5498999999999999</v>
+        <v>0.5420820276497696</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-122</v>
+        <v>-118</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>-117</v>
@@ -9634,7 +9634,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 55.0% (fair -122). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.3138</v>
+        <v>0.3129</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>108</v>
@@ -9700,7 +9700,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 31.4% (fair +219). Your call.</t>
+          <t>Model 31.3% (fair +220). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9736,10 +9736,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6861999999999999</v>
+        <v>0.6871</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-219</v>
+        <v>-220</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>113</v>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 68.6% (fair -219). Your call.</t>
+          <t>Model 68.7% (fair -220). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9802,10 +9802,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.42375</v>
+        <v>0.405390625</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>156</v>
@@ -9832,7 +9832,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 40.5% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9868,10 +9868,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5762548672566372</v>
+        <v>0.5945973451327434</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-136</v>
+        <v>-147</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>-126</v>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 59.5% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9934,13 +9934,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4737768240343348</v>
+        <v>0.4795154185022026</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 48.0% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -10000,13 +10000,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5262362068965517</v>
+        <v>0.5204502183406113</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-111</v>
+        <v>-109</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-132</v>
+        <v>-129</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 52.0% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -10066,13 +10066,13 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5019</v>
+        <v>0.4415</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-101</v>
+        <v>127</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 44.1% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -10132,10 +10132,10 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4981</v>
+        <v>0.5585</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>101</v>
+        <v>-127</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>113</v>
@@ -10162,7 +10162,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 55.9% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -10198,13 +10198,13 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.33372</v>
+        <v>0.324609375</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -10228,7 +10228,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 33.4% (fair +200). Your call.</t>
+          <t>Model 32.5% (fair +208). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -10264,10 +10264,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.6663046511627908</v>
+        <v>0.6753976744186047</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-200</v>
+        <v>-208</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>-115</v>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 66.6% (fair -200). Your call.</t>
+          <t>Model 67.5% (fair -208). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -10330,13 +10330,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.3767326732673267</v>
+        <v>0.3771475409836066</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>165</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -10396,7 +10396,7 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.6232702970297029</v>
+        <v>0.6228683168316831</v>
       </c>
       <c r="G18" s="14" t="n">
         <v>-165</v>
@@ -10462,10 +10462,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4527</v>
+        <v>0.3947</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>121</v>
+        <v>153</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>105</v>
@@ -10492,7 +10492,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 39.5% (fair +153). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -10528,10 +10528,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5473</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-121</v>
+        <v>-153</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>108</v>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 60.5% (fair -153). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -10594,13 +10594,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4740666666666666</v>
+        <v>0.4757711538461538</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-104</v>
+        <v>-108</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -10624,7 +10624,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -10660,13 +10660,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.525911330049261</v>
+        <v>0.5242233009708738</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-111</v>
+        <v>-110</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -10690,7 +10690,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10726,7 +10726,7 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5780986175115207</v>
+        <v>0.5784760368663594</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>-137</v>
@@ -10792,7 +10792,7 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4219069767441861</v>
+        <v>0.4214883720930233</v>
       </c>
       <c r="G24" s="14" t="n">
         <v>137</v>
@@ -10822,7 +10822,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 42.2% (fair +137). Your call.</t>
+          <t>Model 42.1% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10858,13 +10858,13 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5232</v>
+        <v>0.4884891089108911</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-110</v>
+        <v>105</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>104</v>
+        <v>-102</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10888,7 +10888,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10924,13 +10924,13 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4768</v>
+        <v>0.5115</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>110</v>
+        <v>-105</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +110). Your call.</t>
+          <t>Model 51.1% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10990,13 +10990,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4628378378378379</v>
+        <v>0.4664976958525346</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -11020,7 +11020,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 46.6% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -11056,10 +11056,10 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5371636363636363</v>
+        <v>0.5335090909090908</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-116</v>
+        <v>-114</v>
       </c>
       <c r="H28" s="15" t="n">
         <v>-120</v>
@@ -11086,7 +11086,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 53.4% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -11194,7 +11194,7 @@
         <v>-105</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -11254,13 +11254,13 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.3808614232209738</v>
+        <v>0.3808518518518518</v>
       </c>
       <c r="G31" s="14" t="n">
         <v>163</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -11320,13 +11320,13 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.6191481481481481</v>
+        <v>0.6191636363636364</v>
       </c>
       <c r="G32" s="14" t="n">
         <v>-163</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -11386,13 +11386,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.52095</v>
+        <v>0.5195544554455446</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>-109</v>
+        <v>-108</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -11416,7 +11416,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -11452,13 +11452,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.4790465346534653</v>
+        <v>0.48045</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-102</v>
+        <v>100</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -11482,7 +11482,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -11518,10 +11518,10 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.3872</v>
+        <v>0.3603</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="H35" s="15" t="n">
         <v>127</v>
@@ -11548,7 +11548,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 38.7% (fair +158). Your call.</t>
+          <t>Model 36.0% (fair +178). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -11584,13 +11584,13 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.6128</v>
+        <v>0.6396999999999999</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-158</v>
+        <v>-178</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -11614,7 +11614,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 61.3% (fair -158). Your call.</t>
+          <t>Model 64.0% (fair -178). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -11650,10 +11650,10 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.3081454545454545</v>
+        <v>0.3046909090909091</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H37" s="15" t="n">
         <v>175</v>
@@ -11680,7 +11680,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 30.8% (fair +225). Your call.</t>
+          <t>Model 30.5% (fair +228). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -11716,10 +11716,10 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.6918631178707224</v>
+        <v>0.6952851711026616</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-225</v>
+        <v>-228</v>
       </c>
       <c r="H38" s="15" t="n">
         <v>163</v>
@@ -11746,7 +11746,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 69.2% (fair -225). Your call.</t>
+          <t>Model 69.5% (fair -228). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -11782,13 +11782,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.570844537815126</v>
+        <v>0.5678576271186441</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>-133</v>
+        <v>-131</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>-138</v>
+        <v>-136</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -11812,7 +11812,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 56.8% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -11848,13 +11848,13 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.4291596638655463</v>
+        <v>0.4321276595744681</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -11878,7 +11878,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 42.9% (fair +133). Your call.</t>
+          <t>Model 43.2% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -11920,7 +11920,7 @@
         <v>121</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -12046,7 +12046,7 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.5102</v>
+        <v>0.50975</v>
       </c>
       <c r="G43" s="14" t="n">
         <v>-104</v>
@@ -12112,13 +12112,13 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.4898019801980198</v>
+        <v>0.4902487562189056</v>
       </c>
       <c r="G44" s="14" t="n">
         <v>104</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -12178,10 +12178,10 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.4668</v>
+        <v>0.441</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="H45" s="15" t="n">
         <v>100</v>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 46.7% (fair +114). Your call.</t>
+          <t>Model 44.1% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -12244,13 +12244,13 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.5332</v>
+        <v>0.5589999999999999</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-114</v>
+        <v>-127</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 55.9% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -12310,13 +12310,13 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.456</v>
+        <v>0.4566</v>
       </c>
       <c r="G47" s="14" t="n">
         <v>119</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -12340,7 +12340,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +119). Your call.</t>
+          <t>Model 45.7% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -12376,7 +12376,7 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.544</v>
+        <v>0.5434</v>
       </c>
       <c r="G48" s="14" t="n">
         <v>-119</v>
@@ -12406,7 +12406,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -119). Your call.</t>
+          <t>Model 54.3% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -12442,10 +12442,10 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.4934</v>
+        <v>0.4762</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="H49" s="15" t="n">
         <v>117</v>
@@ -12472,7 +12472,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -12508,13 +12508,13 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.5065999999999999</v>
+        <v>0.5238</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-103</v>
+        <v>-110</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -12538,7 +12538,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -12574,10 +12574,10 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.404</v>
+        <v>0.4010877192982456</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H51" s="15" t="n">
         <v>185</v>
@@ -12604,7 +12604,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 40.4% (fair +148). Your call.</t>
+          <t>Model 40.1% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -12640,13 +12640,13 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.596</v>
+        <v>0.5989090909090909</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-148</v>
+        <v>-149</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -12670,7 +12670,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 59.6% (fair -148). Your call.</t>
+          <t>Model 59.9% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -12706,10 +12706,10 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4400881057268722</v>
+        <v>0.4423348017621145</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H53" s="15" t="n">
         <v>127</v>
@@ -12736,7 +12736,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 44.0% (fair +127). Your call.</t>
+          <t>Model 44.2% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -12772,10 +12772,10 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5599189427312775</v>
+        <v>0.5576810572687225</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-127</v>
+        <v>-126</v>
       </c>
       <c r="H54" s="15" t="n">
         <v>-127</v>
@@ -12802,7 +12802,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 56.0% (fair -127). Your call.</t>
+          <t>Model 55.8% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -12838,10 +12838,10 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.4920230769230769</v>
+        <v>0.4750961538461538</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="H55" s="15" t="n">
         <v>-108</v>
@@ -12868,7 +12868,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 47.5% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -12904,13 +12904,13 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.5079523809523809</v>
+        <v>0.5249038461538462</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-103</v>
+        <v>-110</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -12934,7 +12934,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 52.5% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -12970,10 +12970,10 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.4316</v>
+        <v>0.42424</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H57" s="15" t="n">
         <v>150</v>
@@ -13000,7 +13000,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 43.2% (fair +132). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -13036,13 +13036,13 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5684</v>
+        <v>0.5757488372093024</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-132</v>
+        <v>-136</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 56.8% (fair -132). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -13102,10 +13102,10 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>-201</v>
+        <v>-196</v>
       </c>
       <c r="H59" s="15" t="n"/>
       <c r="I59" s="13">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 66.8% (fair -201). Your call.</t>
+          <t>Model 66.2% (fair -196). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -13166,10 +13166,10 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.3322</v>
+        <v>0.3382</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="H60" s="15" t="n"/>
       <c r="I60" s="13">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 33.2% (fair +201). Your call.</t>
+          <t>Model 33.8% (fair +196). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -13230,10 +13230,10 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.3892</v>
+        <v>0.3931</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H61" s="15" t="n"/>
       <c r="I61" s="13">
@@ -13258,7 +13258,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 38.9% (fair +157). Your call.</t>
+          <t>Model 39.3% (fair +154). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -13294,10 +13294,10 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.6108</v>
+        <v>0.6069</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-157</v>
+        <v>-154</v>
       </c>
       <c r="H62" s="15" t="n"/>
       <c r="I62" s="13">
@@ -13322,7 +13322,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 61.1% (fair -157). Your call.</t>
+          <t>Model 60.7% (fair -154). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -13358,7 +13358,7 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.5405</v>
+        <v>0.5416</v>
       </c>
       <c r="G63" s="14" t="n">
         <v>-118</v>
@@ -13386,7 +13386,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -118). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -13422,7 +13422,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.4595</v>
+        <v>0.4583</v>
       </c>
       <c r="G64" s="14" t="n">
         <v>118</v>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +118). Your call.</t>
+          <t>Model 45.8% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -13486,13 +13486,13 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.6188788381742738</v>
+        <v>0.6208524590163935</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>-162</v>
+        <v>-164</v>
       </c>
       <c r="H65" s="15" t="n">
-        <v>-141</v>
+        <v>-144</v>
       </c>
       <c r="I65" s="13">
         <f>IF($H$65="","",IF($H$65&lt;0,-$H$65/(-$H$65+100),100/($H$65+100)))</f>
@@ -13516,7 +13516,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 61.9% (fair -162). Your call.</t>
+          <t>Model 62.1% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -13552,13 +13552,13 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.3811344537815126</v>
+        <v>0.3791803278688525</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H66" s="15" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="I66" s="13">
         <f>IF($H$66="","",IF($H$66&lt;0,-$H$66/(-$H$66+100),100/($H$66+100)))</f>
@@ -13582,7 +13582,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 38.1% (fair +162). Your call.</t>
+          <t>Model 37.9% (fair +164). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -13618,10 +13618,10 @@
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.53095</v>
+        <v>0.50705</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>-113</v>
+        <v>-103</v>
       </c>
       <c r="H67" s="15" t="n">
         <v>100</v>
@@ -13648,7 +13648,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -13684,10 +13684,10 @@
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.4690686274509804</v>
+        <v>0.4929901960784314</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H68" s="15" t="n">
         <v>104</v>
@@ -13714,7 +13714,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 46.9% (fair +113). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -13750,13 +13750,13 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.4848920187793427</v>
+        <v>0.491924644549763</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H69" s="15" t="n">
-        <v>-113</v>
+        <v>-111</v>
       </c>
       <c r="I69" s="13">
         <f>IF($H$69="","",IF($H$69&lt;0,-$H$69/(-$H$69+100),100/($H$69+100)))</f>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -13816,13 +13816,13 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.5151</v>
+        <v>0.5080882352941176</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>-106</v>
+        <v>-103</v>
       </c>
       <c r="H70" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I70" s="13">
         <f>IF($H$70="","",IF($H$70&lt;0,-$H$70/(-$H$70+100),100/($H$70+100)))</f>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.426640625</v>
+        <v>0.426796875</v>
       </c>
       <c r="G71" s="14" t="n">
         <v>134</v>
@@ -13948,13 +13948,13 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5733569169960474</v>
+        <v>0.573178125</v>
       </c>
       <c r="G72" s="14" t="n">
         <v>-134</v>
       </c>
       <c r="H72" s="15" t="n">
-        <v>-153</v>
+        <v>-156</v>
       </c>
       <c r="I72" s="13">
         <f>IF($H$72="","",IF($H$72&lt;0,-$H$72/(-$H$72+100),100/($H$72+100)))</f>
@@ -14010,17 +14010,17 @@
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Over 10.5</t>
+          <t>Over 10</t>
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.445</v>
+        <v>0.466609756097561</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>117</v>
+        <v>-105</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -14044,7 +14044,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 44.5% (fair +125). Your call.</t>
+          <t>Model 46.7% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -14076,17 +14076,17 @@
       </c>
       <c r="E74" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Under 10</t>
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.5549999999999999</v>
+        <v>0.5333823529411765</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>-125</v>
+        <v>-114</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I74" s="13">
         <f>IF($H$74="","",IF($H$74&lt;0,-$H$74/(-$H$74+100),100/($H$74+100)))</f>
@@ -14110,7 +14110,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 53.3% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -14146,13 +14146,13 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.4103947368421052</v>
+        <v>0.4089224137931034</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -14176,7 +14176,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 41.0% (fair +144). Your call.</t>
+          <t>Model 40.9% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -14212,13 +14212,13 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.5895877551020408</v>
+        <v>0.5910806722689076</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-144</v>
+        <v>-145</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>-145</v>
+        <v>-138</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -14242,7 +14242,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 59.1% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -14278,13 +14278,13 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.50685</v>
+        <v>0.5121999999999999</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>-103</v>
+        <v>-105</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.4931188118811881</v>
+        <v>0.4877941176470588</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H78" s="15" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -14374,7 +14374,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -14410,13 +14410,13 @@
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.5995</v>
+        <v>0.5403</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>-150</v>
+        <v>-118</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -14440,7 +14440,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 60.0% (fair -150). Your call.</t>
+          <t>Model 54.0% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -14476,13 +14476,13 @@
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.4005</v>
+        <v>0.4597</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -14506,7 +14506,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 40.0% (fair +150). Your call.</t>
+          <t>Model 46.0% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -14542,13 +14542,13 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.6132022813688213</v>
+        <v>0.6073031250000001</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>-159</v>
+        <v>-155</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>-163</v>
+        <v>-156</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -14572,7 +14572,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 61.3% (fair -159). Your call.</t>
+          <t>Model 60.7% (fair -155). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -14608,13 +14608,13 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.386796875</v>
+        <v>0.39272</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -14638,7 +14638,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 38.7% (fair +159). Your call.</t>
+          <t>Model 39.3% (fair +155). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -14674,13 +14674,13 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4206722689075631</v>
+        <v>0.4125819672131147</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -14704,7 +14704,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 42.1% (fair +138). Your call.</t>
+          <t>Model 41.3% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -14740,13 +14740,13 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5793100840336134</v>
+        <v>0.5873901639344262</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-138</v>
+        <v>-142</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>-138</v>
+        <v>-144</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -14770,7 +14770,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 57.9% (fair -138). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -14806,13 +14806,13 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.4997076923076923</v>
+        <v>0.5109682464454977</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>-108</v>
+        <v>-111</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -14836,7 +14836,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair +100). Your call.</t>
+          <t>Model 51.1% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -14872,13 +14872,13 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5002941176470588</v>
+        <v>0.4890384615384616</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-100</v>
+        <v>104</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -14902,7 +14902,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair -100). Your call.</t>
+          <t>Model 48.9% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -14938,7 +14938,7 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.4149590163934426</v>
+        <v>0.4142622950819672</v>
       </c>
       <c r="G87" s="14" t="n">
         <v>141</v>
@@ -14968,7 +14968,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 41.5% (fair +141). Your call.</t>
+          <t>Model 41.4% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -15004,13 +15004,13 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.5850306122448979</v>
+        <v>0.58578</v>
       </c>
       <c r="G88" s="14" t="n">
         <v>-141</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>-145</v>
+        <v>-150</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -15034,7 +15034,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 58.5% (fair -141). Your call.</t>
+          <t>Model 58.6% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -15070,13 +15070,13 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.5016589861751153</v>
+        <v>0.5075586854460093</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>-101</v>
+        <v>-103</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -15100,7 +15100,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -15136,13 +15136,13 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.4983552995391705</v>
+        <v>0.4924674418604651</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H90" s="15" t="n">
-        <v>-117</v>
+        <v>-115</v>
       </c>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
@@ -15166,7 +15166,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -15202,10 +15202,10 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.4923557692307692</v>
+        <v>0.4828846153846154</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="H91" s="15" t="n">
         <v>108</v>
@@ -15232,7 +15232,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 48.3% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -15268,10 +15268,10 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.507663184079602</v>
+        <v>0.5171601990049751</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>-103</v>
+        <v>-107</v>
       </c>
       <c r="H92" s="15" t="n">
         <v>-101</v>
@@ -15298,7 +15298,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -15334,13 +15334,13 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.3052651515151516</v>
+        <v>0.2969402985074627</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="H93" s="15" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I93" s="13">
         <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
@@ -15364,7 +15364,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 30.5% (fair +228). Your call.</t>
+          <t>Model 29.7% (fair +237). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -15400,10 +15400,10 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.6947407407407407</v>
+        <v>0.703037037037037</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>-228</v>
+        <v>-237</v>
       </c>
       <c r="H94" s="15" t="n">
         <v>170</v>
@@ -15430,7 +15430,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 69.5% (fair -228). Your call.</t>
+          <t>Model 70.3% (fair -237). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -15466,10 +15466,10 @@
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.49755</v>
+        <v>0.4989</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H95" s="15" t="n">
         <v>100</v>
@@ -15496,7 +15496,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 49.9% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -15532,10 +15532,10 @@
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.50245</v>
+        <v>0.5011</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>-101</v>
+        <v>-100</v>
       </c>
       <c r="H96" s="15" t="n">
         <v>100</v>
@@ -15562,7 +15562,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 50.1% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -15598,10 +15598,10 @@
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.6342</v>
+        <v>0.5089201877934273</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>-173</v>
+        <v>-104</v>
       </c>
       <c r="H97" s="15" t="n">
         <v>113</v>
@@ -15628,7 +15628,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 63.4% (fair -173). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -15664,13 +15664,13 @@
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.3658</v>
+        <v>0.4910767441860466</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>173</v>
+        <v>104</v>
       </c>
       <c r="H98" s="15" t="n">
-        <v>102</v>
+        <v>-115</v>
       </c>
       <c r="I98" s="13">
         <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
@@ -15694,7 +15694,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 36.6% (fair +173). Your call.</t>
+          <t>Model 49.1% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -15730,13 +15730,13 @@
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.6279925925925925</v>
+        <v>0.6322201438848921</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>-169</v>
+        <v>-172</v>
       </c>
       <c r="H99" s="15" t="n">
-        <v>-170</v>
+        <v>-178</v>
       </c>
       <c r="I99" s="13">
         <f>IF($H$99="","",IF($H$99&lt;0,-$H$99/(-$H$99+100),100/($H$99+100)))</f>
@@ -15760,7 +15760,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 62.8% (fair -169). Your call.</t>
+          <t>Model 63.2% (fair -172). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -15796,13 +15796,13 @@
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.3719771863117871</v>
+        <v>0.3677902621722847</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H100" s="15" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
@@ -15826,7 +15826,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 37.2% (fair +169). Your call.</t>
+          <t>Model 36.8% (fair +172). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -15862,7 +15862,7 @@
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.4498678414096917</v>
+        <v>0.4496035242290748</v>
       </c>
       <c r="G101" s="14" t="n">
         <v>122</v>
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.5501519313304721</v>
+        <v>0.5503802575107296</v>
       </c>
       <c r="G102" s="14" t="n">
         <v>-122</v>
@@ -15990,17 +15990,17 @@
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.4655</v>
+        <v>0.5157519230769231</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>115</v>
+        <v>-107</v>
       </c>
       <c r="H103" s="15" t="n">
-        <v>127</v>
+        <v>-108</v>
       </c>
       <c r="I103" s="13">
         <f>IF($H$103="","",IF($H$103&lt;0,-$H$103/(-$H$103+100),100/($H$103+100)))</f>
@@ -16024,7 +16024,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -16056,14 +16056,14 @@
       </c>
       <c r="E104" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.5345</v>
+        <v>0.48425</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>-115</v>
+        <v>107</v>
       </c>
       <c r="H104" s="15" t="n">
         <v>100</v>
@@ -16090,7 +16090,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -16126,13 +16126,13 @@
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.3788212927756654</v>
+        <v>0.380546875</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H105" s="15" t="n">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="I105" s="13">
         <f>IF($H$105="","",IF($H$105&lt;0,-$H$105/(-$H$105+100),100/($H$105+100)))</f>
@@ -16156,7 +16156,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 37.9% (fair +164). Your call.</t>
+          <t>Model 38.1% (fair +163). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -16192,10 +16192,10 @@
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.6211925925925925</v>
+        <v>0.6194296296296296</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>-164</v>
+        <v>-163</v>
       </c>
       <c r="H106" s="15" t="n">
         <v>-170</v>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 62.1% (fair -164). Your call.</t>
+          <t>Model 61.9% (fair -163). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -16258,13 +16258,13 @@
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.4331932773109243</v>
+        <v>0.4331147540983606</v>
       </c>
       <c r="G107" s="14" t="n">
         <v>131</v>
       </c>
       <c r="H107" s="15" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="I107" s="13">
         <f>IF($H$107="","",IF($H$107&lt;0,-$H$107/(-$H$107+100),100/($H$107+100)))</f>
@@ -16324,13 +16324,13 @@
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.5667857142857142</v>
+        <v>0.5668524590163935</v>
       </c>
       <c r="G108" s="14" t="n">
         <v>-131</v>
       </c>
       <c r="H108" s="15" t="n">
-        <v>-138</v>
+        <v>-144</v>
       </c>
       <c r="I108" s="13">
         <f>IF($H$108="","",IF($H$108&lt;0,-$H$108/(-$H$108+100),100/($H$108+100)))</f>
@@ -16390,10 +16390,10 @@
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>0.526229268292683</v>
+        <v>0.5334512195121952</v>
       </c>
       <c r="G109" s="14" t="n">
-        <v>-111</v>
+        <v>-114</v>
       </c>
       <c r="H109" s="15" t="n">
         <v>-105</v>
@@ -16420,7 +16420,7 @@
       </c>
       <c r="N109" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 53.3% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O109" s="15" t="n"/>
@@ -16456,10 +16456,10 @@
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.4737857142857143</v>
+        <v>0.4665571428571428</v>
       </c>
       <c r="G110" s="14" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H110" s="15" t="n">
         <v>-110</v>
@@ -16486,7 +16486,7 @@
       </c>
       <c r="N110" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 46.7% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O110" s="15" t="n"/>
@@ -16522,10 +16522,10 @@
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>0.4149583333333334</v>
+        <v>0.4062916666666667</v>
       </c>
       <c r="G111" s="14" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="H111" s="15" t="n">
         <v>140</v>
@@ -16552,7 +16552,7 @@
       </c>
       <c r="N111" s="19" t="inlineStr">
         <is>
-          <t>Model 41.5% (fair +141). Your call.</t>
+          <t>Model 40.6% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O111" s="15" t="n"/>
@@ -16588,13 +16588,13 @@
         </is>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.5850833333333332</v>
+        <v>0.5936714285714286</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>-141</v>
+        <v>-146</v>
       </c>
       <c r="H112" s="15" t="n">
-        <v>-140</v>
+        <v>-145</v>
       </c>
       <c r="I112" s="13">
         <f>IF($H$112="","",IF($H$112&lt;0,-$H$112/(-$H$112+100),100/($H$112+100)))</f>
@@ -16618,7 +16618,7 @@
       </c>
       <c r="N112" s="19" t="inlineStr">
         <is>
-          <t>Model 58.5% (fair -141). Your call.</t>
+          <t>Model 59.4% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O112" s="15" t="n"/>
@@ -16654,13 +16654,13 @@
         </is>
       </c>
       <c r="F113" s="13" t="n">
-        <v>0.4083269961977187</v>
+        <v>0.414296875</v>
       </c>
       <c r="G113" s="14" t="n">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="H113" s="15" t="n">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="I113" s="13">
         <f>IF($H$113="","",IF($H$113&lt;0,-$H$113/(-$H$113+100),100/($H$113+100)))</f>
@@ -16684,7 +16684,7 @@
       </c>
       <c r="N113" s="19" t="inlineStr">
         <is>
-          <t>Model 40.8% (fair +145). Your call.</t>
+          <t>Model 41.4% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O113" s="15" t="n"/>
@@ -16720,13 +16720,13 @@
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.5916709923664122</v>
+        <v>0.5856703125</v>
       </c>
       <c r="G114" s="14" t="n">
-        <v>-145</v>
+        <v>-141</v>
       </c>
       <c r="H114" s="15" t="n">
-        <v>-162</v>
+        <v>-156</v>
       </c>
       <c r="I114" s="13">
         <f>IF($H$114="","",IF($H$114&lt;0,-$H$114/(-$H$114+100),100/($H$114+100)))</f>
@@ -16750,7 +16750,7 @@
       </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
-          <t>Model 59.2% (fair -145). Your call.</t>
+          <t>Model 58.6% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O114" s="15" t="n"/>
@@ -16786,10 +16786,10 @@
         </is>
       </c>
       <c r="F115" s="13" t="n">
-        <v>0.397</v>
+        <v>0.445</v>
       </c>
       <c r="G115" s="14" t="n">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="H115" s="15" t="n">
         <v>108</v>
@@ -16816,7 +16816,7 @@
       </c>
       <c r="N115" s="19" t="inlineStr">
         <is>
-          <t>Model 39.7% (fair +152). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O115" s="15" t="n"/>
@@ -16852,13 +16852,13 @@
         </is>
       </c>
       <c r="F116" s="13" t="n">
-        <v>0.603</v>
+        <v>0.555</v>
       </c>
       <c r="G116" s="14" t="n">
-        <v>-152</v>
+        <v>-125</v>
       </c>
       <c r="H116" s="15" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I116" s="13">
         <f>IF($H$116="","",IF($H$116&lt;0,-$H$116/(-$H$116+100),100/($H$116+100)))</f>
@@ -16882,7 +16882,7 @@
       </c>
       <c r="N116" s="19" t="inlineStr">
         <is>
-          <t>Model 60.3% (fair -152). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O116" s="15" t="n"/>
@@ -16918,7 +16918,7 @@
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>0.4051680672268908</v>
+        <v>0.4049579831932773</v>
       </c>
       <c r="G117" s="14" t="n">
         <v>147</v>
@@ -16984,13 +16984,13 @@
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.5947959183673469</v>
+        <v>0.5950032786885245</v>
       </c>
       <c r="G118" s="14" t="n">
         <v>-147</v>
       </c>
       <c r="H118" s="15" t="n">
-        <v>-145</v>
+        <v>-144</v>
       </c>
       <c r="I118" s="13">
         <f>IF($H$118="","",IF($H$118&lt;0,-$H$118/(-$H$118+100),100/($H$118+100)))</f>
@@ -17178,10 +17178,10 @@
         </is>
       </c>
       <c r="F121" s="13" t="n">
-        <v>0.5839442060085837</v>
+        <v>0.5873690987124464</v>
       </c>
       <c r="G121" s="14" t="n">
-        <v>-140</v>
+        <v>-142</v>
       </c>
       <c r="H121" s="15" t="n">
         <v>-133</v>
@@ -17208,7 +17208,7 @@
       </c>
       <c r="N121" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -140). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O121" s="15" t="n"/>
@@ -17244,13 +17244,13 @@
         </is>
       </c>
       <c r="F122" s="13" t="n">
-        <v>0.4160085836909871</v>
+        <v>0.4126470588235294</v>
       </c>
       <c r="G122" s="14" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H122" s="15" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="I122" s="13">
         <f>IF($H$122="","",IF($H$122&lt;0,-$H$122/(-$H$122+100),100/($H$122+100)))</f>
@@ -17274,7 +17274,7 @@
       </c>
       <c r="N122" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +140). Your call.</t>
+          <t>Model 41.3% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O122" s="15" t="n"/>
@@ -17316,7 +17316,7 @@
         <v>135</v>
       </c>
       <c r="H123" s="15" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="I123" s="13">
         <f>IF($H$123="","",IF($H$123&lt;0,-$H$123/(-$H$123+100),100/($H$123+100)))</f>
@@ -17382,7 +17382,7 @@
         <v>-135</v>
       </c>
       <c r="H124" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I124" s="13">
         <f>IF($H$124="","",IF($H$124&lt;0,-$H$124/(-$H$124+100),100/($H$124+100)))</f>
@@ -17442,13 +17442,13 @@
         </is>
       </c>
       <c r="F125" s="13" t="n">
-        <v>0.5411766519823789</v>
+        <v>0.5341090909090909</v>
       </c>
       <c r="G125" s="14" t="n">
-        <v>-118</v>
+        <v>-115</v>
       </c>
       <c r="H125" s="15" t="n">
-        <v>-127</v>
+        <v>-120</v>
       </c>
       <c r="I125" s="13">
         <f>IF($H$125="","",IF($H$125&lt;0,-$H$125/(-$H$125+100),100/($H$125+100)))</f>
@@ -17472,7 +17472,7 @@
       </c>
       <c r="N125" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 53.4% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O125" s="15" t="n"/>
@@ -17508,13 +17508,13 @@
         </is>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.4588018433179724</v>
+        <v>0.465868544600939</v>
       </c>
       <c r="G126" s="14" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H126" s="15" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I126" s="13">
         <f>IF($H$126="","",IF($H$126&lt;0,-$H$126/(-$H$126+100),100/($H$126+100)))</f>
@@ -17538,7 +17538,7 @@
       </c>
       <c r="N126" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O126" s="15" t="n"/>
@@ -17700,17 +17700,17 @@
       </c>
       <c r="E129" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F129" s="13" t="n">
-        <v>0.5202</v>
+        <v>0.5406230769230769</v>
       </c>
       <c r="G129" s="14" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H129" s="15" t="n">
         <v>-108</v>
-      </c>
-      <c r="H129" s="15" t="n">
-        <v>127</v>
       </c>
       <c r="I129" s="13">
         <f>IF($H$129="","",IF($H$129&lt;0,-$H$129/(-$H$129+100),100/($H$129+100)))</f>
@@ -17734,7 +17734,7 @@
       </c>
       <c r="N129" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O129" s="15" t="n"/>
@@ -17766,14 +17766,14 @@
       </c>
       <c r="E130" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F130" s="13" t="n">
-        <v>0.4798</v>
+        <v>0.4594</v>
       </c>
       <c r="G130" s="14" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="H130" s="15" t="n">
         <v>100</v>
@@ -17800,7 +17800,7 @@
       </c>
       <c r="N130" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O130" s="15" t="n"/>
@@ -18299,10 +18299,10 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>0.2504</v>
+        <v>0.2505</v>
       </c>
       <c r="D5" s="21" t="n">
         <v>215</v>
@@ -18330,10 +18330,10 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>0.252</v>
+        <v>0.2521</v>
       </c>
       <c r="D6" s="21" t="n">
         <v>176</v>
@@ -18434,7 +18434,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>When the model said X%, how often it actually happened (n=271, ECE 0.052 — lower is better; a calibrated model's bars sit on the diagonal).</t>
+          <t>When the model said X%, how often it actually happened (n=272, ECE 0.054 — lower is better; a calibrated model's bars sit on the diagonal).</t>
         </is>
       </c>
     </row>
@@ -18548,16 +18548,16 @@
         </is>
       </c>
       <c r="B21" s="21" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>0.5423</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>0.5294</v>
+        <v>0.5243</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>-0.0129</v>
+        <v>-0.018</v>
       </c>
     </row>
     <row r="22">
@@ -18753,7 +18753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q84"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18770,170 +18770,320 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals offense vs Chicago Cubs defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B69" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C69" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D69" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E69" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F69" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G69" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H69" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I69" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J69" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K69" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L69" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M69" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N69" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O69" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P69" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q69" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="70">
-      <c r="A70" s="29" t="inlineStr">
-        <is>
-          <t>St. Louis Cardinals offense vs Chicago Cubs defense</t>
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>4.473</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="H70" s="33" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>4.653</v>
+      </c>
+      <c r="Q70" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B71" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C71" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D71" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E71" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F71" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G71" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H71" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I71" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J71" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K71" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L71" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M71" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N71" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O71" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P71" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q71" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A71" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B71" s="32" t="n">
+        <v>7.826</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>7.896</v>
+      </c>
+      <c r="Q71" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>4.473</v>
+        <v>1.109</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="D72" s="32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E72" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="F72" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="G72" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="H72" s="33" t="inlineStr">
-        <is>
-          <t>18th</t>
+        <v>1</v>
+      </c>
+      <c r="D72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="34" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L72" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="M72" s="32" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="N72" s="32" t="n">
-        <v>3.9</v>
+      <c r="J72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O72" s="32" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>4.653</v>
+        <v>1.354</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>7.826</v>
+        <v>8.196</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D73" s="32" t="inlineStr">
         <is>
@@ -18987,398 +19137,398 @@
         </is>
       </c>
       <c r="O73" s="32" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>7.896</v>
+        <v>7.708</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>1.109</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="C74" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.867</v>
+      </c>
+      <c r="D74" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E74" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F74" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G74" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J74" s="33" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L74" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M74" s="32" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="N74" s="32" t="n">
+        <v>0.1</v>
       </c>
       <c r="O74" s="32" t="n">
-        <v>1</v>
+        <v>0.433</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>1.354</v>
+        <v>0.446</v>
       </c>
       <c r="Q74" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>8.196</v>
-      </c>
-      <c r="C75" s="32" t="n">
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>Chicago Cubs offense vs St. Louis Cardinals defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B77" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C77" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D77" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E77" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F77" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G77" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H77" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I77" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J77" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K77" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L77" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M77" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N77" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O77" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P77" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q77" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>5.867</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>7.933</v>
+      </c>
+      <c r="F78" s="32" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="D75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H75" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>7.708</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B76" s="32" t="n">
-        <v>0.5629999999999999</v>
-      </c>
-      <c r="C76" s="32" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="D76" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E76" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F76" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G76" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H76" s="34" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J76" s="33" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L76" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M76" s="32" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="N76" s="32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O76" s="32" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="P76" s="32" t="n">
-        <v>0.446</v>
-      </c>
-      <c r="Q76" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="29" t="inlineStr">
-        <is>
-          <t>Chicago Cubs offense vs St. Louis Cardinals defense</t>
+      <c r="G78" s="32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="O78" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>4.568</v>
+      </c>
+      <c r="Q78" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B79" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C79" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D79" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E79" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F79" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G79" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H79" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I79" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J79" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K79" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L79" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M79" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N79" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O79" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P79" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q79" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A79" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B79" s="32" t="n">
+        <v>8.438000000000001</v>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr"/>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="P79" s="32" t="n">
+        <v>8.651999999999999</v>
+      </c>
+      <c r="Q79" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>5.32</v>
+        <v>1.104</v>
       </c>
       <c r="C80" s="32" t="n">
-        <v>5.867</v>
-      </c>
-      <c r="D80" s="32" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="E80" s="32" t="n">
-        <v>7.933</v>
-      </c>
-      <c r="F80" s="32" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="G80" s="32" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="H80" s="34" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="I80" s="32" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J80" s="34" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="K80" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L80" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="M80" s="32" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="N80" s="32" t="n">
-        <v>5.15</v>
+        <v>0.75</v>
+      </c>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="32" t="inlineStr"/>
+      <c r="J80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O80" s="32" t="n">
-        <v>4.6</v>
+        <v>0.6</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>4.568</v>
+        <v>1.043</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>8.438000000000001</v>
+        <v>8.458</v>
       </c>
       <c r="C81" s="32" t="n">
-        <v>8.5</v>
+        <v>7.25</v>
       </c>
       <c r="D81" s="32" t="inlineStr">
         <is>
@@ -19432,225 +19582,75 @@
         </is>
       </c>
       <c r="O81" s="32" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>8.651999999999999</v>
+        <v>7.739</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B82" s="32" t="n">
-        <v>1.104</v>
+        <v>0.459</v>
       </c>
       <c r="C82" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D82" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E82" s="32" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="F82" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G82" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H82" s="33" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="I82" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J82" s="36" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L82" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M82" s="32" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="N82" s="32" t="n">
         <v>0.75</v>
       </c>
-      <c r="D82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O82" s="32" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>1.043</v>
+        <v>0.606</v>
       </c>
       <c r="Q82" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B83" s="32" t="n">
-        <v>8.458</v>
-      </c>
-      <c r="C83" s="32" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="D83" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E83" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F83" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G83" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H83" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I83" s="32" t="inlineStr"/>
-      <c r="J83" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K83" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L83" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M83" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N83" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O83" s="32" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="P83" s="32" t="n">
-        <v>7.739</v>
-      </c>
-      <c r="Q83" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B84" s="32" t="n">
-        <v>0.459</v>
-      </c>
-      <c r="C84" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D84" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E84" s="32" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="F84" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G84" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H84" s="33" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="I84" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J84" s="36" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="K84" s="32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="L84" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M84" s="32" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="N84" s="32" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O84" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P84" s="32" t="n">
-        <v>0.606</v>
-      </c>
-      <c r="Q84" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -19669,7 +19669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19686,170 +19686,245 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates offense vs Washington Nationals defense</t>
+        </is>
+      </c>
+    </row>
     <row r="68">
-      <c r="A68" s="29" t="inlineStr">
-        <is>
-          <t>Pittsburgh Pirates offense vs Washington Nationals defense</t>
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B69" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C69" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D69" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E69" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F69" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G69" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H69" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I69" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J69" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K69" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L69" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M69" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N69" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O69" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P69" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q69" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>5.062</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>6.067</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H69" s="34" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr"/>
+      <c r="J69" s="34" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>4.733</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>5.103</v>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>5.062</v>
+        <v>8.811999999999999</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>5.667</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>6.067</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H70" s="34" t="inlineStr">
-        <is>
-          <t>5th</t>
+        <v>12</v>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="34" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>4.733</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>4.95</v>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O70" s="32" t="n">
-        <v>4.533</v>
+        <v>7.5</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>5.103</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>8.811999999999999</v>
+        <v>1.188</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>12</v>
+        <v>2.667</v>
       </c>
       <c r="D71" s="32" t="inlineStr">
         <is>
@@ -19903,28 +19978,28 @@
         </is>
       </c>
       <c r="O71" s="32" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>9.039999999999999</v>
+        <v>1.56</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>1.188</v>
+        <v>9.708</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>2.667</v>
+        <v>8.333</v>
       </c>
       <c r="D72" s="32" t="inlineStr">
         <is>
@@ -19978,319 +20053,319 @@
         </is>
       </c>
       <c r="O72" s="32" t="n">
-        <v>2.5</v>
+        <v>8.25</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>1.56</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>9.708</v>
+        <v>0.547</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>8.333</v>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.4</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="36" t="inlineStr">
+        <is>
+          <t>30th</t>
         </is>
       </c>
       <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="36" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>0.5</v>
       </c>
       <c r="O73" s="32" t="n">
-        <v>8.25</v>
+        <v>0.4</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>8.199999999999999</v>
+        <v>0.408</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>0.547</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D74" s="32" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E74" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F74" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G74" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="36" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="36" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="L74" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M74" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N74" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>0.408</v>
-      </c>
-      <c r="Q74" s="35" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>Washington Nationals offense vs Pittsburgh Pirates defense</t>
+        </is>
+      </c>
+    </row>
     <row r="76">
-      <c r="A76" s="29" t="inlineStr">
-        <is>
-          <t>Washington Nationals offense vs Pittsburgh Pirates defense</t>
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B77" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C77" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D77" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E77" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F77" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G77" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H77" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I77" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J77" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K77" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L77" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M77" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N77" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O77" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P77" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q77" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>5.282</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>4.733</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H77" s="34" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J77" s="36" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>4.733</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O77" s="32" t="n">
+        <v>5.633</v>
+      </c>
+      <c r="P77" s="32" t="n">
+        <v>4.763</v>
+      </c>
+      <c r="Q77" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>5.282</v>
+        <v>8.52</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>4.733</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H78" s="34" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J78" s="36" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>4.733</v>
-      </c>
-      <c r="N78" s="32" t="n">
-        <v>5.2</v>
+        <v>7.75</v>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O78" s="32" t="n">
-        <v>5.633</v>
+        <v>8.667</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>4.763</v>
+        <v>7.792</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>8.52</v>
+        <v>1.26</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>7.75</v>
+        <v>1</v>
       </c>
       <c r="D79" s="32" t="inlineStr">
         <is>
@@ -20344,28 +20419,28 @@
         </is>
       </c>
       <c r="O79" s="32" t="n">
-        <v>8.667</v>
+        <v>1</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>7.792</v>
+        <v>0.896</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>1.26</v>
+        <v>7.98</v>
       </c>
       <c r="C80" s="32" t="n">
-        <v>1</v>
+        <v>6.75</v>
       </c>
       <c r="D80" s="32" t="inlineStr">
         <is>
@@ -20419,146 +20494,71 @@
         </is>
       </c>
       <c r="O80" s="32" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>0.896</v>
+        <v>9.292</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>7.98</v>
+        <v>0.829</v>
       </c>
       <c r="C81" s="32" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.633</v>
+      </c>
+      <c r="D81" s="32" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E81" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F81" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G81" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H81" s="33" t="inlineStr">
+        <is>
+          <t>15th</t>
         </is>
       </c>
       <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J81" s="33" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L81" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M81" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N81" s="32" t="n">
+        <v>0.45</v>
       </c>
       <c r="O81" s="32" t="n">
-        <v>11</v>
+        <v>0.433</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>9.292</v>
+        <v>0.4</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="n">
-        <v>0.829</v>
-      </c>
-      <c r="C82" s="32" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="D82" s="32" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E82" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F82" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G82" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H82" s="33" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="33" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L82" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M82" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N82" s="32" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="O82" s="32" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -20577,7 +20577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20594,174 +20594,249 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>Minnesota Twins offense vs New York Yankees defense</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>Minnesota Twins offense vs New York Yankees defense</t>
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B69" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C69" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D69" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E69" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F69" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G69" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H69" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I69" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J69" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K69" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L69" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M69" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N69" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O69" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P69" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q69" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>4.813</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>6.067</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H70" s="33" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J70" s="36" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>5.133</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>4.633</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>3.766</v>
+      </c>
+      <c r="Q70" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>4.813</v>
+        <v>7.776</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>5.533</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>6.067</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="H71" s="33" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J71" s="36" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>5.133</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>4.75</v>
+        <v>9.5</v>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O71" s="32" t="n">
-        <v>4.633</v>
+        <v>10</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>3.766</v>
+        <v>7.609</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>7.776</v>
+        <v>1.061</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>9.5</v>
+        <v>0.75</v>
       </c>
       <c r="D72" s="32" t="inlineStr">
         <is>
@@ -20815,28 +20890,28 @@
         </is>
       </c>
       <c r="O72" s="32" t="n">
-        <v>10</v>
+        <v>1.75</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>7.609</v>
+        <v>0.913</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>1.061</v>
+        <v>8.939</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>0.75</v>
+        <v>8.5</v>
       </c>
       <c r="D73" s="32" t="inlineStr">
         <is>
@@ -20890,319 +20965,319 @@
         </is>
       </c>
       <c r="O73" s="32" t="n">
-        <v>1.75</v>
+        <v>8.25</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>0.913</v>
+        <v>8.435</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>8.939</v>
+        <v>0.68</v>
       </c>
       <c r="C74" s="32" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="D74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.8</v>
+      </c>
+      <c r="D74" s="32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E74" s="32" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="F74" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G74" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J74" s="36" t="inlineStr">
+        <is>
+          <t>28th</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L74" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M74" s="32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="N74" s="32" t="n">
+        <v>0.6</v>
       </c>
       <c r="O74" s="32" t="n">
-        <v>8.25</v>
+        <v>0.6</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>8.435</v>
+        <v>0.472</v>
       </c>
       <c r="Q74" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H75" s="34" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J75" s="36" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>0.472</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>New York Yankees offense vs Minnesota Twins defense</t>
+        </is>
+      </c>
+    </row>
     <row r="77">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>New York Yankees offense vs Minnesota Twins defense</t>
+      <c r="A77" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B77" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C77" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D77" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E77" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F77" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G77" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H77" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I77" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J77" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K77" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L77" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M77" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N77" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O77" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P77" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q77" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A78" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>4.567</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>3.133</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H78" s="36" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="33" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="O78" s="32" t="n">
+        <v>5.933</v>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>5.133</v>
+      </c>
+      <c r="Q78" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>4.74</v>
+        <v>8.109</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>4.567</v>
-      </c>
-      <c r="D79" s="32" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E79" s="32" t="n">
-        <v>3.133</v>
-      </c>
-      <c r="F79" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G79" s="32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H79" s="36" t="inlineStr">
-        <is>
-          <t>29th</t>
+        <v>9.25</v>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="33" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L79" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M79" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="N79" s="32" t="n">
-        <v>5.55</v>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O79" s="32" t="n">
-        <v>5.933</v>
+        <v>10.5</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>5.133</v>
+        <v>8.305999999999999</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>8.109</v>
+        <v>1.413</v>
       </c>
       <c r="C80" s="32" t="n">
-        <v>9.25</v>
+        <v>1</v>
       </c>
       <c r="D80" s="32" t="inlineStr">
         <is>
@@ -21256,28 +21331,28 @@
         </is>
       </c>
       <c r="O80" s="32" t="n">
-        <v>10.5</v>
+        <v>2</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>8.305999999999999</v>
+        <v>0.918</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>1.413</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="C81" s="32" t="n">
-        <v>1</v>
+        <v>8.75</v>
       </c>
       <c r="D81" s="32" t="inlineStr">
         <is>
@@ -21331,146 +21406,71 @@
         </is>
       </c>
       <c r="O81" s="32" t="n">
-        <v>2</v>
+        <v>9.75</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>0.918</v>
+        <v>8.265000000000001</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B82" s="32" t="n">
-        <v>9.130000000000001</v>
+        <v>0.625</v>
       </c>
       <c r="C82" s="32" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="D82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.433</v>
+      </c>
+      <c r="D82" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E82" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F82" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G82" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H82" s="36" t="inlineStr">
+        <is>
+          <t>24th</t>
         </is>
       </c>
       <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J82" s="33" t="inlineStr">
+        <is>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L82" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M82" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="N82" s="32" t="n">
+        <v>0.45</v>
       </c>
       <c r="O82" s="32" t="n">
-        <v>9.75</v>
+        <v>0.633</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>8.265000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="Q82" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="32" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="C83" s="32" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="D83" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E83" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F83" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G83" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H83" s="36" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="I83" s="32" t="inlineStr"/>
-      <c r="J83" s="33" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="K83" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L83" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M83" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="N83" s="32" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="O83" s="32" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="P83" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q83" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
